--- a/unova_progression.xlsx
+++ b/unova_progression.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F419"/>
+  <dimension ref="A1:F409"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -635,7 +635,7 @@
         <v>Azurill</v>
       </c>
       <c r="E12" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F12" t="str">
         <v>12.5%</v>
@@ -655,7 +655,7 @@
         <v>Buizel</v>
       </c>
       <c r="E13" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F13" t="str">
         <v>12.5%</v>
@@ -675,7 +675,7 @@
         <v>Jellicent</v>
       </c>
       <c r="E14" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F14" t="str">
         <v>12.5%</v>
@@ -695,7 +695,7 @@
         <v>Magikarp</v>
       </c>
       <c r="E15" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F15" t="str">
         <v>12.5%</v>
@@ -715,7 +715,7 @@
         <v>Seel</v>
       </c>
       <c r="E16" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F16" t="str">
         <v>12.5%</v>
@@ -735,7 +735,7 @@
         <v>Frillish</v>
       </c>
       <c r="E17" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F17" t="str">
         <v>12.5%</v>
@@ -755,7 +755,7 @@
         <v>Staryu</v>
       </c>
       <c r="E18" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F18" t="str">
         <v>12.5%</v>
@@ -775,7 +775,7 @@
         <v>Horsea</v>
       </c>
       <c r="E19" t="str">
-        <v>5-6</v>
+        <v>4-5</v>
       </c>
       <c r="F19" t="str">
         <v>12.5%</v>
@@ -1075,7 +1075,7 @@
         <v>Marill</v>
       </c>
       <c r="E34" t="str">
-        <v>11-12</v>
+        <v>10-11</v>
       </c>
       <c r="F34" t="str">
         <v>14.26%</v>
@@ -1095,7 +1095,7 @@
         <v>Remoraid</v>
       </c>
       <c r="E35" t="str">
-        <v>11-12</v>
+        <v>10-11</v>
       </c>
       <c r="F35" t="str">
         <v>14.29%</v>
@@ -1115,7 +1115,7 @@
         <v>Mantyke</v>
       </c>
       <c r="E36" t="str">
-        <v>11-12</v>
+        <v>10-11</v>
       </c>
       <c r="F36" t="str">
         <v>14.29%</v>
@@ -1135,7 +1135,7 @@
         <v>Basculin</v>
       </c>
       <c r="E37" t="str">
-        <v>11-12</v>
+        <v>10-11</v>
       </c>
       <c r="F37" t="str">
         <v>14.29%</v>
@@ -1155,7 +1155,7 @@
         <v>Clamperl</v>
       </c>
       <c r="E38" t="str">
-        <v>11-12</v>
+        <v>10-11</v>
       </c>
       <c r="F38" t="str">
         <v>14.29%</v>
@@ -1175,7 +1175,7 @@
         <v>Krabby</v>
       </c>
       <c r="E39" t="str">
-        <v>11-12</v>
+        <v>10-11</v>
       </c>
       <c r="F39" t="str">
         <v>14.29%</v>
@@ -1195,7 +1195,7 @@
         <v>Spheal</v>
       </c>
       <c r="E40" t="str">
-        <v>11-12</v>
+        <v>10-11</v>
       </c>
       <c r="F40" t="str">
         <v>14.29%</v>
@@ -1215,7 +1215,7 @@
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>12-13</v>
+        <v>11-12</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>17-18</v>
+        <v>16-17</v>
       </c>
       <c r="F62" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Drilbur</v>
       </c>
       <c r="E63" t="str">
-        <v>18-19</v>
+        <v>17-18</v>
       </c>
       <c r="F63" t="str">
         <v>25%</v>
@@ -1675,7 +1675,7 @@
         <v>Woobat</v>
       </c>
       <c r="E64" t="str">
-        <v>18-19</v>
+        <v>17-18</v>
       </c>
       <c r="F64" t="str">
         <v>25%</v>
@@ -1695,7 +1695,7 @@
         <v>Rattata</v>
       </c>
       <c r="E65" t="str">
-        <v>18-19</v>
+        <v>17-18</v>
       </c>
       <c r="F65" t="str">
         <v>25%</v>
@@ -1715,7 +1715,7 @@
         <v>Timburr</v>
       </c>
       <c r="E66" t="str">
-        <v>18-19</v>
+        <v>17-18</v>
       </c>
       <c r="F66" t="str">
         <v>25%</v>
@@ -1735,7 +1735,7 @@
         <v>Darumaka</v>
       </c>
       <c r="E67" t="str">
-        <v>19-20</v>
+        <v>18-19</v>
       </c>
       <c r="F67" t="str">
         <v>25%</v>
@@ -1755,7 +1755,7 @@
         <v>Sandile</v>
       </c>
       <c r="E68" t="str">
-        <v>19-20</v>
+        <v>18-19</v>
       </c>
       <c r="F68" t="str">
         <v>25%</v>
@@ -1775,7 +1775,7 @@
         <v>Trubbish</v>
       </c>
       <c r="E69" t="str">
-        <v>19-20</v>
+        <v>18-19</v>
       </c>
       <c r="F69" t="str">
         <v>25%</v>
@@ -1795,7 +1795,7 @@
         <v>Scraggy</v>
       </c>
       <c r="E70" t="str">
-        <v>19-20</v>
+        <v>18-19</v>
       </c>
       <c r="F70" t="str">
         <v>25%</v>
@@ -2015,7 +2015,7 @@
         <v>Yamask</v>
       </c>
       <c r="E81" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F81" t="str">
         <v>11.12%</v>
@@ -2035,7 +2035,7 @@
         <v>Sandile</v>
       </c>
       <c r="E82" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F82" t="str">
         <v>11.11%</v>
@@ -2055,7 +2055,7 @@
         <v>Trubbish</v>
       </c>
       <c r="E83" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F83" t="str">
         <v>11.11%</v>
@@ -2075,7 +2075,7 @@
         <v>Archen</v>
       </c>
       <c r="E84" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F84" t="str">
         <v>11.11%</v>
@@ -2095,7 +2095,7 @@
         <v>Baltoy</v>
       </c>
       <c r="E85" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F85" t="str">
         <v>11.11%</v>
@@ -2115,7 +2115,7 @@
         <v>Larvesta</v>
       </c>
       <c r="E86" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F86" t="str">
         <v>11.11%</v>
@@ -2135,7 +2135,7 @@
         <v>Cofagrigus</v>
       </c>
       <c r="E87" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F87" t="str">
         <v>11.11%</v>
@@ -2155,7 +2155,7 @@
         <v>Krookodile</v>
       </c>
       <c r="E88" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F88" t="str">
         <v>11.11%</v>
@@ -2175,7 +2175,7 @@
         <v>Volcarona</v>
       </c>
       <c r="E89" t="str">
-        <v>22-23</v>
+        <v>21-22</v>
       </c>
       <c r="F89" t="str">
         <v>11.11%</v>
@@ -2195,7 +2195,7 @@
         <v>Pachirisu</v>
       </c>
       <c r="E90" t="str">
-        <v>23-24</v>
+        <v>22-23</v>
       </c>
       <c r="F90" t="str">
         <v>33.34%</v>
@@ -2215,7 +2215,7 @@
         <v>Plusle</v>
       </c>
       <c r="E91" t="str">
-        <v>23-24</v>
+        <v>22-23</v>
       </c>
       <c r="F91" t="str">
         <v>33.33%</v>
@@ -2235,7 +2235,7 @@
         <v>Minun</v>
       </c>
       <c r="E92" t="str">
-        <v>23-24</v>
+        <v>22-23</v>
       </c>
       <c r="F92" t="str">
         <v>33.33%</v>
@@ -2255,7 +2255,7 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>24-25</v>
+        <v>23-24</v>
       </c>
       <c r="F93" t="str">
         <v/>
@@ -2275,7 +2275,7 @@
         <v>Gothitelle</v>
       </c>
       <c r="E94" t="str">
-        <v>25-26</v>
+        <v>24-25</v>
       </c>
       <c r="F94" t="str">
         <v>16.65%</v>
@@ -2295,7 +2295,7 @@
         <v>Reuniclus</v>
       </c>
       <c r="E95" t="str">
-        <v>25-26</v>
+        <v>24-25</v>
       </c>
       <c r="F95" t="str">
         <v>16.67%</v>
@@ -2315,7 +2315,7 @@
         <v>Trubbish</v>
       </c>
       <c r="E96" t="str">
-        <v>25-26</v>
+        <v>24-25</v>
       </c>
       <c r="F96" t="str">
         <v>16.67%</v>
@@ -2335,7 +2335,7 @@
         <v>Foongus</v>
       </c>
       <c r="E97" t="str">
-        <v>25-26</v>
+        <v>24-25</v>
       </c>
       <c r="F97" t="str">
         <v>16.67%</v>
@@ -2355,7 +2355,7 @@
         <v>Emolga</v>
       </c>
       <c r="E98" t="str">
-        <v>25-26</v>
+        <v>24-25</v>
       </c>
       <c r="F98" t="str">
         <v>16.67%</v>
@@ -2375,7 +2375,7 @@
         <v>Joltik</v>
       </c>
       <c r="E99" t="str">
-        <v>25-26</v>
+        <v>24-25</v>
       </c>
       <c r="F99" t="str">
         <v>16.67%</v>
@@ -2395,7 +2395,7 @@
         <v>Heracross</v>
       </c>
       <c r="E100" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F100" t="str">
         <v>10%</v>
@@ -2415,7 +2415,7 @@
         <v>Pinsir</v>
       </c>
       <c r="E101" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F101" t="str">
         <v>10%</v>
@@ -2435,7 +2435,7 @@
         <v>Gothita</v>
       </c>
       <c r="E102" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F102" t="str">
         <v>10%</v>
@@ -2455,7 +2455,7 @@
         <v>Minccino</v>
       </c>
       <c r="E103" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F103" t="str">
         <v>10%</v>
@@ -2475,7 +2475,7 @@
         <v>Trubbish</v>
       </c>
       <c r="E104" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F104" t="str">
         <v>10%</v>
@@ -2495,7 +2495,7 @@
         <v>Solosis</v>
       </c>
       <c r="E105" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F105" t="str">
         <v>10%</v>
@@ -2515,7 +2515,7 @@
         <v>Slakoth</v>
       </c>
       <c r="E106" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F106" t="str">
         <v>10%</v>
@@ -2535,7 +2535,7 @@
         <v>Leavanny</v>
       </c>
       <c r="E107" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F107" t="str">
         <v>10%</v>
@@ -2555,7 +2555,7 @@
         <v>Cinccino</v>
       </c>
       <c r="E108" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F108" t="str">
         <v>10%</v>
@@ -2575,7 +2575,7 @@
         <v>Unfezant</v>
       </c>
       <c r="E109" t="str">
-        <v>26-27</v>
+        <v>25-26</v>
       </c>
       <c r="F109" t="str">
         <v>10%</v>
@@ -2595,7 +2595,7 @@
         <v>Remoraid</v>
       </c>
       <c r="E110" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F110" t="str">
         <v>12.5%</v>
@@ -2615,7 +2615,7 @@
         <v>Carvanha</v>
       </c>
       <c r="E111" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F111" t="str">
         <v>12.5%</v>
@@ -2635,7 +2635,7 @@
         <v>Chinchou</v>
       </c>
       <c r="E112" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F112" t="str">
         <v>12.5%</v>
@@ -2655,7 +2655,7 @@
         <v>Finneon</v>
       </c>
       <c r="E113" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F113" t="str">
         <v>12.5%</v>
@@ -2675,7 +2675,7 @@
         <v>Goldeen</v>
       </c>
       <c r="E114" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F114" t="str">
         <v>12.5%</v>
@@ -2695,7 +2695,7 @@
         <v>Luvdisc</v>
       </c>
       <c r="E115" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F115" t="str">
         <v>12.5%</v>
@@ -2715,7 +2715,7 @@
         <v>Shellder</v>
       </c>
       <c r="E116" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F116" t="str">
         <v>12.5%</v>
@@ -2735,7 +2735,7 @@
         <v>Swanna</v>
       </c>
       <c r="E117" t="str">
-        <v>28-29</v>
+        <v>27-28</v>
       </c>
       <c r="F117" t="str">
         <v>12.5%</v>
@@ -2775,7 +2775,7 @@
         <v>Deerling</v>
       </c>
       <c r="E119" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F119" t="str">
         <v>10%</v>
@@ -2795,7 +2795,7 @@
         <v>Karrablast</v>
       </c>
       <c r="E120" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F120" t="str">
         <v>10%</v>
@@ -2815,7 +2815,7 @@
         <v>Trubbish</v>
       </c>
       <c r="E121" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F121" t="str">
         <v>10%</v>
@@ -2835,7 +2835,7 @@
         <v>Foongus</v>
       </c>
       <c r="E122" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F122" t="str">
         <v>10%</v>
@@ -2855,7 +2855,7 @@
         <v>Vanillite</v>
       </c>
       <c r="E123" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F123" t="str">
         <v>10%</v>
@@ -2875,7 +2875,7 @@
         <v>Castform</v>
       </c>
       <c r="E124" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F124" t="str">
         <v>10%</v>
@@ -2895,7 +2895,7 @@
         <v>Swadloon</v>
       </c>
       <c r="E125" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F125" t="str">
         <v>10%</v>
@@ -2915,7 +2915,7 @@
         <v>Sawsbuck</v>
       </c>
       <c r="E126" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F126" t="str">
         <v>10%</v>
@@ -2935,7 +2935,7 @@
         <v>Escavalier</v>
       </c>
       <c r="E127" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F127" t="str">
         <v>10%</v>
@@ -2955,7 +2955,7 @@
         <v>Accelgor</v>
       </c>
       <c r="E128" t="str">
-        <v>30-31</v>
+        <v>29-30</v>
       </c>
       <c r="F128" t="str">
         <v>10%</v>
@@ -2975,7 +2975,7 @@
         <v>Joltik</v>
       </c>
       <c r="E129" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F129" t="str">
         <v>12.5%</v>
@@ -2995,7 +2995,7 @@
         <v>Klink</v>
       </c>
       <c r="E130" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F130" t="str">
         <v>12.5%</v>
@@ -3015,7 +3015,7 @@
         <v>Ferroseed</v>
       </c>
       <c r="E131" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F131" t="str">
         <v>12.5%</v>
@@ -3035,7 +3035,7 @@
         <v>Tynamo</v>
       </c>
       <c r="E132" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F132" t="str">
         <v>12.5%</v>
@@ -3055,7 +3055,7 @@
         <v>Aron</v>
       </c>
       <c r="E133" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F133" t="str">
         <v>12.5%</v>
@@ -3075,7 +3075,7 @@
         <v>Magneton</v>
       </c>
       <c r="E134" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F134" t="str">
         <v>12.5%</v>
@@ -3095,7 +3095,7 @@
         <v>Klang</v>
       </c>
       <c r="E135" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F135" t="str">
         <v>12.5%</v>
@@ -3115,7 +3115,7 @@
         <v>Galvantula</v>
       </c>
       <c r="E136" t="str">
-        <v>31-32</v>
+        <v>30-31</v>
       </c>
       <c r="F136" t="str">
         <v>12.5%</v>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="E137" t="str">
-        <v>32-33</v>
+        <v>31-32</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -3155,7 +3155,7 @@
         <v>Deerling</v>
       </c>
       <c r="E138" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F138" t="str">
         <v>11.12%</v>
@@ -3175,7 +3175,7 @@
         <v>Watchog</v>
       </c>
       <c r="E139" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F139" t="str">
         <v>11.11%</v>
@@ -3195,7 +3195,7 @@
         <v>Foongus</v>
       </c>
       <c r="E140" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F140" t="str">
         <v>11.11%</v>
@@ -3215,7 +3215,7 @@
         <v>Cubchoo</v>
       </c>
       <c r="E141" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F141" t="str">
         <v>11.11%</v>
@@ -3235,7 +3235,7 @@
         <v>Zebstrika</v>
       </c>
       <c r="E142" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F142" t="str">
         <v>11.11%</v>
@@ -3255,7 +3255,7 @@
         <v>Zangoose</v>
       </c>
       <c r="E143" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F143" t="str">
         <v>11.11%</v>
@@ -3275,7 +3275,7 @@
         <v>Seviper</v>
       </c>
       <c r="E144" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F144" t="str">
         <v>11.11%</v>
@@ -3295,7 +3295,7 @@
         <v>Zoroark</v>
       </c>
       <c r="E145" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F145" t="str">
         <v>11.11%</v>
@@ -3315,7 +3315,7 @@
         <v>Tranquill</v>
       </c>
       <c r="E146" t="str">
-        <v>34-35</v>
+        <v>32-33</v>
       </c>
       <c r="F146" t="str">
         <v>11.11%</v>
@@ -3335,7 +3335,7 @@
         <v>Litwick</v>
       </c>
       <c r="E147" t="str">
-        <v>35-36</v>
+        <v>34-35</v>
       </c>
       <c r="F147" t="str">
         <v>16.65%</v>
@@ -3355,7 +3355,7 @@
         <v>Elgyem</v>
       </c>
       <c r="E148" t="str">
-        <v>35-36</v>
+        <v>34-35</v>
       </c>
       <c r="F148" t="str">
         <v>16.67%</v>
@@ -3375,7 +3375,7 @@
         <v>Golbat</v>
       </c>
       <c r="E149" t="str">
-        <v>35-36</v>
+        <v>34-35</v>
       </c>
       <c r="F149" t="str">
         <v>16.67%</v>
@@ -3395,7 +3395,7 @@
         <v>Lampent</v>
       </c>
       <c r="E150" t="str">
-        <v>35-36</v>
+        <v>34-35</v>
       </c>
       <c r="F150" t="str">
         <v>16.67%</v>
@@ -3415,7 +3415,7 @@
         <v>Musharna</v>
       </c>
       <c r="E151" t="str">
-        <v>35-36</v>
+        <v>34-35</v>
       </c>
       <c r="F151" t="str">
         <v>16.67%</v>
@@ -3435,7 +3435,7 @@
         <v>Swoobat</v>
       </c>
       <c r="E152" t="str">
-        <v>35-36</v>
+        <v>34-35</v>
       </c>
       <c r="F152" t="str">
         <v>16.67%</v>
@@ -3475,7 +3475,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>37-38</v>
+        <v>36-37</v>
       </c>
       <c r="F154" t="str">
         <v/>
@@ -3495,7 +3495,7 @@
         <v>Skarmory</v>
       </c>
       <c r="E155" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F155" t="str">
         <v>11.12%</v>
@@ -3515,7 +3515,7 @@
         <v>Camerupt</v>
       </c>
       <c r="E156" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F156" t="str">
         <v>11.11%</v>
@@ -3535,7 +3535,7 @@
         <v>Excadrill</v>
       </c>
       <c r="E157" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F157" t="str">
         <v>11.11%</v>
@@ -3555,7 +3555,7 @@
         <v>Lopunny</v>
       </c>
       <c r="E158" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F158" t="str">
         <v>11.11%</v>
@@ -3575,7 +3575,7 @@
         <v>Skorupi</v>
       </c>
       <c r="E159" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F159" t="str">
         <v>11.11%</v>
@@ -3595,7 +3595,7 @@
         <v>Numel</v>
       </c>
       <c r="E160" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F160" t="str">
         <v>11.11%</v>
@@ -3615,7 +3615,7 @@
         <v>Magmar</v>
       </c>
       <c r="E161" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F161" t="str">
         <v>11.11%</v>
@@ -3635,7 +3635,7 @@
         <v>Vibrava</v>
       </c>
       <c r="E162" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F162" t="str">
         <v>11.11%</v>
@@ -3655,7 +3655,7 @@
         <v>Flygon</v>
       </c>
       <c r="E163" t="str">
-        <v>38-39</v>
+        <v>37-38</v>
       </c>
       <c r="F163" t="str">
         <v>11.11%</v>
@@ -3675,7 +3675,7 @@
         <v>Litwick</v>
       </c>
       <c r="E164" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F164" t="str">
         <v>10%</v>
@@ -3695,7 +3695,7 @@
         <v>Raticate</v>
       </c>
       <c r="E165" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F165" t="str">
         <v>10%</v>
@@ -3715,7 +3715,7 @@
         <v>Golbat</v>
       </c>
       <c r="E166" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F166" t="str">
         <v>10%</v>
@@ -3735,7 +3735,7 @@
         <v>Banette</v>
       </c>
       <c r="E167" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F167" t="str">
         <v>10%</v>
@@ -3755,7 +3755,7 @@
         <v>Gothita</v>
       </c>
       <c r="E168" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F168" t="str">
         <v>10%</v>
@@ -3775,7 +3775,7 @@
         <v>Solosis</v>
       </c>
       <c r="E169" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F169" t="str">
         <v>10%</v>
@@ -3795,7 +3795,7 @@
         <v>Gothorita</v>
       </c>
       <c r="E170" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F170" t="str">
         <v>10%</v>
@@ -3815,7 +3815,7 @@
         <v>Duosion</v>
       </c>
       <c r="E171" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F171" t="str">
         <v>10%</v>
@@ -3835,7 +3835,7 @@
         <v>Shuppet</v>
       </c>
       <c r="E172" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F172" t="str">
         <v>10%</v>
@@ -3855,7 +3855,7 @@
         <v>Chandelure</v>
       </c>
       <c r="E173" t="str">
-        <v>40-41</v>
+        <v>38-39</v>
       </c>
       <c r="F173" t="str">
         <v>10%</v>
@@ -3895,7 +3895,7 @@
         <v>Barboach</v>
       </c>
       <c r="E175" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F175" t="str">
         <v>8.37%</v>
@@ -3915,7 +3915,7 @@
         <v>Poliwag</v>
       </c>
       <c r="E176" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F176" t="str">
         <v>8.33%</v>
@@ -3935,7 +3935,7 @@
         <v>Buizel</v>
       </c>
       <c r="E177" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F177" t="str">
         <v>8.33%</v>
@@ -3955,7 +3955,7 @@
         <v>Lumineon</v>
       </c>
       <c r="E178" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F178" t="str">
         <v>8.33%</v>
@@ -3975,7 +3975,7 @@
         <v>Corphish</v>
       </c>
       <c r="E179" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F179" t="str">
         <v>8.33%</v>
@@ -3995,7 +3995,7 @@
         <v>Frillish</v>
       </c>
       <c r="E180" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F180" t="str">
         <v>8.33%</v>
@@ -4015,7 +4015,7 @@
         <v>Kingler</v>
       </c>
       <c r="E181" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F181" t="str">
         <v>8.33%</v>
@@ -4035,7 +4035,7 @@
         <v>Marill</v>
       </c>
       <c r="E182" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F182" t="str">
         <v>8.33%</v>
@@ -4055,7 +4055,7 @@
         <v>Wailmer</v>
       </c>
       <c r="E183" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F183" t="str">
         <v>8.33%</v>
@@ -4075,7 +4075,7 @@
         <v>Mantine</v>
       </c>
       <c r="E184" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F184" t="str">
         <v>8.33%</v>
@@ -4095,7 +4095,7 @@
         <v>Starmie</v>
       </c>
       <c r="E185" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F185" t="str">
         <v>8.33%</v>
@@ -4115,7 +4115,7 @@
         <v>Wailord</v>
       </c>
       <c r="E186" t="str">
-        <v>42-43</v>
+        <v>41-42</v>
       </c>
       <c r="F186" t="str">
         <v>8.33%</v>
@@ -4135,7 +4135,7 @@
         <v>Tangela</v>
       </c>
       <c r="E187" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F187" t="str">
         <v>12.5%</v>
@@ -4155,7 +4155,7 @@
         <v>Drifblim</v>
       </c>
       <c r="E188" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F188" t="str">
         <v>12.5%</v>
@@ -4175,7 +4175,7 @@
         <v>Pelipper</v>
       </c>
       <c r="E189" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F189" t="str">
         <v>12.5%</v>
@@ -4195,7 +4195,7 @@
         <v>Absol</v>
       </c>
       <c r="E190" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F190" t="str">
         <v>12.5%</v>
@@ -4215,7 +4215,7 @@
         <v>Floatzel</v>
       </c>
       <c r="E191" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F191" t="str">
         <v>12.5%</v>
@@ -4235,7 +4235,7 @@
         <v>Drifloon</v>
       </c>
       <c r="E192" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F192" t="str">
         <v>12.5%</v>
@@ -4255,7 +4255,7 @@
         <v>Swanna</v>
       </c>
       <c r="E193" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F193" t="str">
         <v>12.5%</v>
@@ -4275,7 +4275,7 @@
         <v>Seismitoad</v>
       </c>
       <c r="E194" t="str">
-        <v>43-44</v>
+        <v>42-43</v>
       </c>
       <c r="F194" t="str">
         <v>12.5%</v>
@@ -4295,7 +4295,7 @@
         <v>Altaria</v>
       </c>
       <c r="E195" t="str">
-        <v>44-45</v>
+        <v>43-44</v>
       </c>
       <c r="F195" t="str">
         <v>16.65%</v>
@@ -4315,7 +4315,7 @@
         <v>Absol</v>
       </c>
       <c r="E196" t="str">
-        <v>44-45</v>
+        <v>43-44</v>
       </c>
       <c r="F196" t="str">
         <v>16.67%</v>
@@ -4335,7 +4335,7 @@
         <v>Mienfoo</v>
       </c>
       <c r="E197" t="str">
-        <v>44-45</v>
+        <v>43-44</v>
       </c>
       <c r="F197" t="str">
         <v>16.67%</v>
@@ -4355,7 +4355,7 @@
         <v>Golduck</v>
       </c>
       <c r="E198" t="str">
-        <v>44-45</v>
+        <v>43-44</v>
       </c>
       <c r="F198" t="str">
         <v>16.67%</v>
@@ -4375,7 +4375,7 @@
         <v>Swablu</v>
       </c>
       <c r="E199" t="str">
-        <v>44-45</v>
+        <v>43-44</v>
       </c>
       <c r="F199" t="str">
         <v>16.67%</v>
@@ -4395,7 +4395,7 @@
         <v>Tropius</v>
       </c>
       <c r="E200" t="str">
-        <v>44-45</v>
+        <v>43-44</v>
       </c>
       <c r="F200" t="str">
         <v>16.67%</v>
@@ -4415,7 +4415,7 @@
         <v>Vulpix</v>
       </c>
       <c r="E201" t="str">
-        <v>46-47</v>
+        <v>44-45</v>
       </c>
       <c r="F201" t="str">
         <v>20%</v>
@@ -4435,7 +4435,7 @@
         <v>Bronzong</v>
       </c>
       <c r="E202" t="str">
-        <v>46-47</v>
+        <v>44-45</v>
       </c>
       <c r="F202" t="str">
         <v>20%</v>
@@ -4455,7 +4455,7 @@
         <v>Swablu</v>
       </c>
       <c r="E203" t="str">
-        <v>46-47</v>
+        <v>44-45</v>
       </c>
       <c r="F203" t="str">
         <v>20%</v>
@@ -4475,7 +4475,7 @@
         <v>Chimecho</v>
       </c>
       <c r="E204" t="str">
-        <v>46-47</v>
+        <v>44-45</v>
       </c>
       <c r="F204" t="str">
         <v>20%</v>
@@ -4495,7 +4495,7 @@
         <v>Gothitelle</v>
       </c>
       <c r="E205" t="str">
-        <v>46-47</v>
+        <v>44-45</v>
       </c>
       <c r="F205" t="str">
         <v>20%</v>
@@ -4535,7 +4535,7 @@
         <v/>
       </c>
       <c r="E207" t="str">
-        <v>48-49</v>
+        <v>46-47</v>
       </c>
       <c r="F207" t="str">
         <v/>
@@ -4555,7 +4555,7 @@
         <v>Gligar</v>
       </c>
       <c r="E208" t="str">
-        <v>49-50</v>
+        <v>48-49</v>
       </c>
       <c r="F208" t="str">
         <v>20%</v>
@@ -4575,7 +4575,7 @@
         <v>Zangoose</v>
       </c>
       <c r="E209" t="str">
-        <v>49-50</v>
+        <v>48-49</v>
       </c>
       <c r="F209" t="str">
         <v>20%</v>
@@ -4595,7 +4595,7 @@
         <v>Seviper</v>
       </c>
       <c r="E210" t="str">
-        <v>49-50</v>
+        <v>48-49</v>
       </c>
       <c r="F210" t="str">
         <v>20%</v>
@@ -4615,7 +4615,7 @@
         <v>Karrablast</v>
       </c>
       <c r="E211" t="str">
-        <v>49-50</v>
+        <v>48-49</v>
       </c>
       <c r="F211" t="str">
         <v>20%</v>
@@ -4635,7 +4635,7 @@
         <v>Shelmet</v>
       </c>
       <c r="E212" t="str">
-        <v>49-50</v>
+        <v>48-49</v>
       </c>
       <c r="F212" t="str">
         <v>20%</v>
@@ -4655,7 +4655,7 @@
         <v>Bibarel</v>
       </c>
       <c r="E213" t="str">
-        <v>51-52</v>
+        <v>49-50</v>
       </c>
       <c r="F213" t="str">
         <v>16.65%</v>
@@ -4675,7 +4675,7 @@
         <v>Zebstrika</v>
       </c>
       <c r="E214" t="str">
-        <v>51-52</v>
+        <v>49-50</v>
       </c>
       <c r="F214" t="str">
         <v>16.67%</v>
@@ -4695,7 +4695,7 @@
         <v>Pelipper</v>
       </c>
       <c r="E215" t="str">
-        <v>51-52</v>
+        <v>49-50</v>
       </c>
       <c r="F215" t="str">
         <v>16.67%</v>
@@ -4715,7 +4715,7 @@
         <v>Dunsparce</v>
       </c>
       <c r="E216" t="str">
-        <v>51-52</v>
+        <v>49-50</v>
       </c>
       <c r="F216" t="str">
         <v>16.67%</v>
@@ -4735,7 +4735,7 @@
         <v>Loudred</v>
       </c>
       <c r="E217" t="str">
-        <v>51-52</v>
+        <v>49-50</v>
       </c>
       <c r="F217" t="str">
         <v>16.67%</v>
@@ -4755,7 +4755,7 @@
         <v>Azumarill</v>
       </c>
       <c r="E218" t="str">
-        <v>51-52</v>
+        <v>49-50</v>
       </c>
       <c r="F218" t="str">
         <v>16.67%</v>
@@ -4775,7 +4775,7 @@
         <v>Sewaddle</v>
       </c>
       <c r="E219" t="str">
-        <v>52-53</v>
+        <v>50-51</v>
       </c>
       <c r="F219" t="str">
         <v>14.26%</v>
@@ -4795,7 +4795,7 @@
         <v>Tranquill</v>
       </c>
       <c r="E220" t="str">
-        <v>52-53</v>
+        <v>50-51</v>
       </c>
       <c r="F220" t="str">
         <v>14.29%</v>
@@ -4815,7 +4815,7 @@
         <v>Roselia</v>
       </c>
       <c r="E221" t="str">
-        <v>52-53</v>
+        <v>50-51</v>
       </c>
       <c r="F221" t="str">
         <v>14.29%</v>
@@ -4835,7 +4835,7 @@
         <v>Combee</v>
       </c>
       <c r="E222" t="str">
-        <v>52-53</v>
+        <v>50-51</v>
       </c>
       <c r="F222" t="str">
         <v>14.29%</v>
@@ -4855,7 +4855,7 @@
         <v>Pinsir</v>
       </c>
       <c r="E223" t="str">
-        <v>52-53</v>
+        <v>50-51</v>
       </c>
       <c r="F223" t="str">
         <v>14.29%</v>
@@ -4875,7 +4875,7 @@
         <v>Sunflora</v>
       </c>
       <c r="E224" t="str">
-        <v>52-53</v>
+        <v>50-51</v>
       </c>
       <c r="F224" t="str">
         <v>14.29%</v>
@@ -4895,7 +4895,7 @@
         <v>Vespiquen</v>
       </c>
       <c r="E225" t="str">
-        <v>52-53</v>
+        <v>50-51</v>
       </c>
       <c r="F225" t="str">
         <v>14.29%</v>
@@ -4915,7 +4915,7 @@
         <v>Garbodor</v>
       </c>
       <c r="E226" t="str">
-        <v>53-54</v>
+        <v>51-52</v>
       </c>
       <c r="F226" t="str">
         <v>16.65%</v>
@@ -4935,7 +4935,7 @@
         <v>Liepard</v>
       </c>
       <c r="E227" t="str">
-        <v>53-54</v>
+        <v>51-52</v>
       </c>
       <c r="F227" t="str">
         <v>16.67%</v>
@@ -4955,7 +4955,7 @@
         <v>Muk</v>
       </c>
       <c r="E228" t="str">
-        <v>53-54</v>
+        <v>51-52</v>
       </c>
       <c r="F228" t="str">
         <v>16.67%</v>
@@ -4975,7 +4975,7 @@
         <v>Minccino</v>
       </c>
       <c r="E229" t="str">
-        <v>53-54</v>
+        <v>51-52</v>
       </c>
       <c r="F229" t="str">
         <v>16.67%</v>
@@ -4995,7 +4995,7 @@
         <v>Duosion</v>
       </c>
       <c r="E230" t="str">
-        <v>53-54</v>
+        <v>51-52</v>
       </c>
       <c r="F230" t="str">
         <v>16.67%</v>
@@ -5015,7 +5015,7 @@
         <v>Gigalith</v>
       </c>
       <c r="E231" t="str">
-        <v>53-54</v>
+        <v>51-52</v>
       </c>
       <c r="F231" t="str">
         <v>16.67%</v>
@@ -5055,7 +5055,7 @@
         <v>Feebas</v>
       </c>
       <c r="E233" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F233" t="str">
         <v>10%</v>
@@ -5075,7 +5075,7 @@
         <v>Finneon</v>
       </c>
       <c r="E234" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F234" t="str">
         <v>10%</v>
@@ -5095,7 +5095,7 @@
         <v>Qwilfish</v>
       </c>
       <c r="E235" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F235" t="str">
         <v>10%</v>
@@ -5115,7 +5115,7 @@
         <v>Stunfisk</v>
       </c>
       <c r="E236" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F236" t="str">
         <v>10%</v>
@@ -5135,7 +5135,7 @@
         <v>Palpitoad</v>
       </c>
       <c r="E237" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F237" t="str">
         <v>10%</v>
@@ -5155,7 +5155,7 @@
         <v>Poliwhirl</v>
       </c>
       <c r="E238" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F238" t="str">
         <v>10%</v>
@@ -5175,7 +5175,7 @@
         <v>Politoed</v>
       </c>
       <c r="E239" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F239" t="str">
         <v>10%</v>
@@ -5195,7 +5195,7 @@
         <v>Sealeo</v>
       </c>
       <c r="E240" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F240" t="str">
         <v>10%</v>
@@ -5215,7 +5215,7 @@
         <v>Walrein</v>
       </c>
       <c r="E241" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F241" t="str">
         <v>10%</v>
@@ -5235,7 +5235,7 @@
         <v>Dewgong</v>
       </c>
       <c r="E242" t="str">
-        <v>55-56</v>
+        <v>53-54</v>
       </c>
       <c r="F242" t="str">
         <v>10%</v>
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="E243" t="str">
-        <v>57-58</v>
+        <v>55-56</v>
       </c>
       <c r="F243" t="str">
         <v/>
@@ -5275,7 +5275,7 @@
         <v>Mantyke</v>
       </c>
       <c r="E244" t="str">
-        <v>58-59</v>
+        <v>56-57</v>
       </c>
       <c r="F244" t="str">
         <v>14.26%</v>
@@ -5295,7 +5295,7 @@
         <v>Luvdisc</v>
       </c>
       <c r="E245" t="str">
-        <v>58-59</v>
+        <v>56-57</v>
       </c>
       <c r="F245" t="str">
         <v>14.29%</v>
@@ -5315,7 +5315,7 @@
         <v>Corsola</v>
       </c>
       <c r="E246" t="str">
-        <v>58-59</v>
+        <v>56-57</v>
       </c>
       <c r="F246" t="str">
         <v>14.29%</v>
@@ -5335,7 +5335,7 @@
         <v>Wingull</v>
       </c>
       <c r="E247" t="str">
-        <v>58-59</v>
+        <v>56-57</v>
       </c>
       <c r="F247" t="str">
         <v>14.29%</v>
@@ -5355,7 +5355,7 @@
         <v>Pelipper</v>
       </c>
       <c r="E248" t="str">
-        <v>58-59</v>
+        <v>56-57</v>
       </c>
       <c r="F248" t="str">
         <v>14.29%</v>
@@ -5375,7 +5375,7 @@
         <v>Octillery</v>
       </c>
       <c r="E249" t="str">
-        <v>58-59</v>
+        <v>56-57</v>
       </c>
       <c r="F249" t="str">
         <v>14.29%</v>
@@ -5395,7 +5395,7 @@
         <v>Crawdaunt</v>
       </c>
       <c r="E250" t="str">
-        <v>58-59</v>
+        <v>56-57</v>
       </c>
       <c r="F250" t="str">
         <v>14.29%</v>
@@ -5415,7 +5415,7 @@
         <v>Boldore</v>
       </c>
       <c r="E251" t="str">
-        <v>59-60</v>
+        <v>57-58</v>
       </c>
       <c r="F251" t="str">
         <v>16.65%</v>
@@ -5435,7 +5435,7 @@
         <v>Feebas</v>
       </c>
       <c r="E252" t="str">
-        <v>59-60</v>
+        <v>57-58</v>
       </c>
       <c r="F252" t="str">
         <v>16.67%</v>
@@ -5455,7 +5455,7 @@
         <v>Alomomola</v>
       </c>
       <c r="E253" t="str">
-        <v>59-60</v>
+        <v>57-58</v>
       </c>
       <c r="F253" t="str">
         <v>16.67%</v>
@@ -5475,7 +5475,7 @@
         <v>Woobat</v>
       </c>
       <c r="E254" t="str">
-        <v>59-60</v>
+        <v>57-58</v>
       </c>
       <c r="F254" t="str">
         <v>16.67%</v>
@@ -5495,7 +5495,7 @@
         <v>Shuckle</v>
       </c>
       <c r="E255" t="str">
-        <v>59-60</v>
+        <v>57-58</v>
       </c>
       <c r="F255" t="str">
         <v>16.67%</v>
@@ -5515,7 +5515,7 @@
         <v>Carracosta</v>
       </c>
       <c r="E256" t="str">
-        <v>59-60</v>
+        <v>57-58</v>
       </c>
       <c r="F256" t="str">
         <v>16.67%</v>
@@ -5535,7 +5535,7 @@
         <v>Pelipper</v>
       </c>
       <c r="E257" t="str">
-        <v>60-61</v>
+        <v>58-59</v>
       </c>
       <c r="F257" t="str">
         <v>25%</v>
@@ -5555,7 +5555,7 @@
         <v>Golduck</v>
       </c>
       <c r="E258" t="str">
-        <v>60-61</v>
+        <v>58-59</v>
       </c>
       <c r="F258" t="str">
         <v>25%</v>
@@ -5575,7 +5575,7 @@
         <v>Marill</v>
       </c>
       <c r="E259" t="str">
-        <v>60-61</v>
+        <v>58-59</v>
       </c>
       <c r="F259" t="str">
         <v>25%</v>
@@ -5595,7 +5595,7 @@
         <v>Amoonguss</v>
       </c>
       <c r="E260" t="str">
-        <v>60-61</v>
+        <v>58-59</v>
       </c>
       <c r="F260" t="str">
         <v>25%</v>
@@ -5606,19 +5606,19 @@
         <v>51</v>
       </c>
       <c r="B261" t="str">
-        <v>Giant Chasm</v>
+        <v>P2 Laboratory</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261" t="str">
-        <v>Delibird</v>
+        <v>Beldum</v>
       </c>
       <c r="E261" t="str">
-        <v>61-62</v>
+        <v>59-60</v>
       </c>
       <c r="F261" t="str">
-        <v>9.1%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="262">
@@ -5626,19 +5626,19 @@
         <v>51</v>
       </c>
       <c r="B262" t="str">
-        <v>Giant Chasm</v>
+        <v>P2 Laboratory</v>
       </c>
       <c r="C262" t="str">
         <v/>
       </c>
       <c r="D262" t="str">
-        <v>Swinub</v>
+        <v>Pawniard</v>
       </c>
       <c r="E262" t="str">
-        <v>61-62</v>
+        <v>59-60</v>
       </c>
       <c r="F262" t="str">
-        <v>9.09%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="263">
@@ -5646,19 +5646,19 @@
         <v>51</v>
       </c>
       <c r="B263" t="str">
-        <v>Giant Chasm</v>
+        <v>P2 Laboratory</v>
       </c>
       <c r="C263" t="str">
         <v/>
       </c>
       <c r="D263" t="str">
-        <v>Piloswine</v>
+        <v>Magnezone</v>
       </c>
       <c r="E263" t="str">
-        <v>61-62</v>
+        <v>59-60</v>
       </c>
       <c r="F263" t="str">
-        <v>9.09%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="264">
@@ -5666,84 +5666,84 @@
         <v>51</v>
       </c>
       <c r="B264" t="str">
-        <v>Giant Chasm</v>
+        <v>P2 Laboratory</v>
       </c>
       <c r="C264" t="str">
         <v/>
       </c>
       <c r="D264" t="str">
-        <v>Ditto</v>
+        <v>Klinklang</v>
       </c>
       <c r="E264" t="str">
-        <v>61-62</v>
+        <v>59-60</v>
       </c>
       <c r="F264" t="str">
-        <v>9.09%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B265" t="str">
-        <v>Giant Chasm</v>
+        <v>Wellspring Cave</v>
       </c>
       <c r="C265" t="str">
         <v/>
       </c>
       <c r="D265" t="str">
-        <v>Clefairy</v>
+        <v>Grimer</v>
       </c>
       <c r="E265" t="str">
-        <v>61-62</v>
+        <v>60-61</v>
       </c>
       <c r="F265" t="str">
-        <v>9.09%</v>
+        <v>33.34%</v>
       </c>
     </row>
     <row r="266">
       <c r="A266">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B266" t="str">
-        <v>Giant Chasm</v>
+        <v>Wellspring Cave</v>
       </c>
       <c r="C266" t="str">
         <v/>
       </c>
       <c r="D266" t="str">
-        <v>Metang</v>
+        <v>Bronzor</v>
       </c>
       <c r="E266" t="str">
-        <v>61-62</v>
+        <v>60-61</v>
       </c>
       <c r="F266" t="str">
-        <v>9.09%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="267">
       <c r="A267">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B267" t="str">
-        <v>Giant Chasm</v>
+        <v>Wellspring Cave</v>
       </c>
       <c r="C267" t="str">
         <v/>
       </c>
       <c r="D267" t="str">
-        <v>Lunatone</v>
+        <v>Weezing</v>
       </c>
       <c r="E267" t="str">
-        <v>61-62</v>
+        <v>60-61</v>
       </c>
       <c r="F267" t="str">
-        <v>9.09%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B268" t="str">
         <v>Giant Chasm</v>
@@ -5752,18 +5752,18 @@
         <v/>
       </c>
       <c r="D268" t="str">
-        <v>Solrock</v>
+        <v>Delibird</v>
       </c>
       <c r="E268" t="str">
-        <v>61-62</v>
+        <v>62-63</v>
       </c>
       <c r="F268" t="str">
-        <v>9.09%</v>
+        <v>9.1%</v>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B269" t="str">
         <v>Giant Chasm</v>
@@ -5772,10 +5772,10 @@
         <v/>
       </c>
       <c r="D269" t="str">
-        <v>Metagross</v>
+        <v>Swinub</v>
       </c>
       <c r="E269" t="str">
-        <v>61-62</v>
+        <v>62-63</v>
       </c>
       <c r="F269" t="str">
         <v>9.09%</v>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B270" t="str">
         <v>Giant Chasm</v>
@@ -5792,10 +5792,10 @@
         <v/>
       </c>
       <c r="D270" t="str">
-        <v>Clefable</v>
+        <v>Piloswine</v>
       </c>
       <c r="E270" t="str">
-        <v>61-62</v>
+        <v>62-63</v>
       </c>
       <c r="F270" t="str">
         <v>9.09%</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B271" t="str">
         <v>Giant Chasm</v>
@@ -5812,10 +5812,10 @@
         <v/>
       </c>
       <c r="D271" t="str">
-        <v>Weavile</v>
+        <v>Ditto</v>
       </c>
       <c r="E271" t="str">
-        <v>61-62</v>
+        <v>62-63</v>
       </c>
       <c r="F271" t="str">
         <v>9.09%</v>
@@ -5823,147 +5823,147 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B272" t="str">
-        <v>Route 23</v>
+        <v>Giant Chasm</v>
       </c>
       <c r="C272" t="str">
         <v/>
       </c>
       <c r="D272" t="str">
-        <v>Sneasel</v>
+        <v>Clefairy</v>
       </c>
       <c r="E272" t="str">
-        <v>63-64</v>
+        <v>62-63</v>
       </c>
       <c r="F272" t="str">
-        <v>11.12%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="273">
       <c r="A273">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B273" t="str">
-        <v>Route 23</v>
+        <v>Giant Chasm</v>
       </c>
       <c r="C273" t="str">
         <v/>
       </c>
       <c r="D273" t="str">
-        <v>Amoonguss</v>
+        <v>Metang</v>
       </c>
       <c r="E273" t="str">
-        <v>63-64</v>
+        <v>62-63</v>
       </c>
       <c r="F273" t="str">
-        <v>11.11%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="274">
       <c r="A274">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B274" t="str">
-        <v>Route 23</v>
+        <v>Giant Chasm</v>
       </c>
       <c r="C274" t="str">
         <v/>
       </c>
       <c r="D274" t="str">
-        <v>Bouffalant</v>
+        <v>Lunatone</v>
       </c>
       <c r="E274" t="str">
-        <v>63-64</v>
+        <v>62-63</v>
       </c>
       <c r="F274" t="str">
-        <v>11.11%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B275" t="str">
-        <v>Route 23</v>
+        <v>Giant Chasm</v>
       </c>
       <c r="C275" t="str">
         <v/>
       </c>
       <c r="D275" t="str">
-        <v>Roserade</v>
+        <v>Solrock</v>
       </c>
       <c r="E275" t="str">
-        <v>63-64</v>
+        <v>62-63</v>
       </c>
       <c r="F275" t="str">
-        <v>11.11%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="276">
       <c r="A276">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B276" t="str">
-        <v>Route 23</v>
+        <v>Giant Chasm</v>
       </c>
       <c r="C276" t="str">
         <v/>
       </c>
       <c r="D276" t="str">
-        <v>Gurdurr</v>
+        <v>Metagross</v>
       </c>
       <c r="E276" t="str">
-        <v>63-64</v>
+        <v>62-63</v>
       </c>
       <c r="F276" t="str">
-        <v>11.11%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="277">
       <c r="A277">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B277" t="str">
-        <v>Route 23</v>
+        <v>Giant Chasm</v>
       </c>
       <c r="C277" t="str">
         <v/>
       </c>
       <c r="D277" t="str">
-        <v>Serperior</v>
+        <v>Clefable</v>
       </c>
       <c r="E277" t="str">
-        <v>63-64</v>
+        <v>62-63</v>
       </c>
       <c r="F277" t="str">
-        <v>11.11%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="278">
       <c r="A278">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B278" t="str">
-        <v>Route 23</v>
+        <v>Giant Chasm</v>
       </c>
       <c r="C278" t="str">
         <v/>
       </c>
       <c r="D278" t="str">
-        <v>Mienshao</v>
+        <v>Weavile</v>
       </c>
       <c r="E278" t="str">
-        <v>63-64</v>
+        <v>62-63</v>
       </c>
       <c r="F278" t="str">
-        <v>11.11%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="279">
       <c r="A279">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B279" t="str">
         <v>Route 23</v>
@@ -5972,18 +5972,18 @@
         <v/>
       </c>
       <c r="D279" t="str">
-        <v>Bisharp</v>
+        <v>Sneasel</v>
       </c>
       <c r="E279" t="str">
         <v>63-64</v>
       </c>
       <c r="F279" t="str">
-        <v>11.11%</v>
+        <v>11.12%</v>
       </c>
     </row>
     <row r="280">
       <c r="A280">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B280" t="str">
         <v>Route 23</v>
@@ -5992,7 +5992,7 @@
         <v/>
       </c>
       <c r="D280" t="str">
-        <v>Gliscor</v>
+        <v>Amoonguss</v>
       </c>
       <c r="E280" t="str">
         <v>63-64</v>
@@ -6003,162 +6003,162 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B281" t="str">
-        <v>Victory Road</v>
+        <v>Route 23</v>
       </c>
       <c r="C281" t="str">
         <v/>
       </c>
       <c r="D281" t="str">
-        <v>Durant</v>
+        <v>Bouffalant</v>
       </c>
       <c r="E281" t="str">
-        <v>64-65</v>
+        <v>63-64</v>
       </c>
       <c r="F281" t="str">
-        <v>14.26%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="282">
       <c r="A282">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B282" t="str">
-        <v>Victory Road</v>
+        <v>Route 23</v>
       </c>
       <c r="C282" t="str">
         <v/>
       </c>
       <c r="D282" t="str">
-        <v>Heatmor</v>
+        <v>Roserade</v>
       </c>
       <c r="E282" t="str">
-        <v>64-65</v>
+        <v>63-64</v>
       </c>
       <c r="F282" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="283">
       <c r="A283">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B283" t="str">
-        <v>Victory Road</v>
+        <v>Route 23</v>
       </c>
       <c r="C283" t="str">
         <v/>
       </c>
       <c r="D283" t="str">
-        <v>Deino</v>
+        <v>Gurdurr</v>
       </c>
       <c r="E283" t="str">
-        <v>64-65</v>
+        <v>63-64</v>
       </c>
       <c r="F283" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="284">
       <c r="A284">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B284" t="str">
-        <v>Victory Road</v>
+        <v>Route 23</v>
       </c>
       <c r="C284" t="str">
         <v/>
       </c>
       <c r="D284" t="str">
-        <v>Druddigon</v>
+        <v>Serperior</v>
       </c>
       <c r="E284" t="str">
-        <v>64-65</v>
+        <v>63-64</v>
       </c>
       <c r="F284" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="285">
       <c r="A285">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B285" t="str">
-        <v>Victory Road</v>
+        <v>Route 23</v>
       </c>
       <c r="C285" t="str">
         <v/>
       </c>
       <c r="D285" t="str">
-        <v>Zweilous</v>
+        <v>Mienshao</v>
       </c>
       <c r="E285" t="str">
-        <v>64-65</v>
+        <v>63-64</v>
       </c>
       <c r="F285" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="286">
       <c r="A286">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B286" t="str">
-        <v>Victory Road</v>
+        <v>Route 23</v>
       </c>
       <c r="C286" t="str">
         <v/>
       </c>
       <c r="D286" t="str">
-        <v>Hydreigon</v>
+        <v>Bisharp</v>
       </c>
       <c r="E286" t="str">
-        <v>64-65</v>
+        <v>63-64</v>
       </c>
       <c r="F286" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="287">
       <c r="A287">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B287" t="str">
-        <v>Victory Road</v>
+        <v>Route 23</v>
       </c>
       <c r="C287" t="str">
         <v/>
       </c>
       <c r="D287" t="str">
-        <v>Golurk</v>
+        <v>Gliscor</v>
       </c>
       <c r="E287" t="str">
-        <v>64-65</v>
+        <v>63-64</v>
       </c>
       <c r="F287" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="288">
       <c r="A288">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B288" t="str">
-        <v>Pokemon League</v>
+        <v>Victory Road</v>
       </c>
       <c r="C288" t="str">
         <v/>
       </c>
       <c r="D288" t="str">
-        <v/>
+        <v>Durant</v>
       </c>
       <c r="E288" t="str">
-        <v>63-65</v>
+        <v>64-65</v>
       </c>
       <c r="F288" t="str">
-        <v/>
+        <v>14.26%</v>
       </c>
     </row>
     <row r="289">
@@ -6166,19 +6166,19 @@
         <v>55</v>
       </c>
       <c r="B289" t="str">
-        <v>Route 8</v>
+        <v>Victory Road</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289" t="str">
-        <v>Palpitoad</v>
+        <v>Heatmor</v>
       </c>
       <c r="E289" t="str">
-        <v>65-66</v>
+        <v>64-65</v>
       </c>
       <c r="F289" t="str">
-        <v>20%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="290">
@@ -6186,19 +6186,19 @@
         <v>55</v>
       </c>
       <c r="B290" t="str">
-        <v>Route 8</v>
+        <v>Victory Road</v>
       </c>
       <c r="C290" t="str">
         <v/>
       </c>
       <c r="D290" t="str">
-        <v>Stunfisk</v>
+        <v>Deino</v>
       </c>
       <c r="E290" t="str">
-        <v>65-66</v>
+        <v>64-65</v>
       </c>
       <c r="F290" t="str">
-        <v>20%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="291">
@@ -6206,19 +6206,19 @@
         <v>55</v>
       </c>
       <c r="B291" t="str">
-        <v>Route 8</v>
+        <v>Victory Road</v>
       </c>
       <c r="C291" t="str">
         <v/>
       </c>
       <c r="D291" t="str">
-        <v>Shellder</v>
+        <v>Druddigon</v>
       </c>
       <c r="E291" t="str">
-        <v>65-66</v>
+        <v>64-65</v>
       </c>
       <c r="F291" t="str">
-        <v>20%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="292">
@@ -6226,19 +6226,19 @@
         <v>55</v>
       </c>
       <c r="B292" t="str">
-        <v>Route 8</v>
+        <v>Victory Road</v>
       </c>
       <c r="C292" t="str">
         <v/>
       </c>
       <c r="D292" t="str">
-        <v>Croagunk</v>
+        <v>Zweilous</v>
       </c>
       <c r="E292" t="str">
-        <v>65-66</v>
+        <v>64-65</v>
       </c>
       <c r="F292" t="str">
-        <v>20%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="293">
@@ -6246,39 +6246,39 @@
         <v>55</v>
       </c>
       <c r="B293" t="str">
-        <v>Route 8</v>
+        <v>Victory Road</v>
       </c>
       <c r="C293" t="str">
         <v/>
       </c>
       <c r="D293" t="str">
-        <v>Crobat</v>
+        <v>Hydreigon</v>
       </c>
       <c r="E293" t="str">
-        <v>65-66</v>
+        <v>64-65</v>
       </c>
       <c r="F293" t="str">
-        <v>20%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="294">
       <c r="A294">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B294" t="str">
-        <v>Moor of Icirrus</v>
+        <v>Victory Road</v>
       </c>
       <c r="C294" t="str">
         <v/>
       </c>
       <c r="D294" t="str">
-        <v>Shelmet</v>
+        <v>Golurk</v>
       </c>
       <c r="E294" t="str">
-        <v>76-77</v>
+        <v>64-65</v>
       </c>
       <c r="F294" t="str">
-        <v>33.34%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="295">
@@ -6286,39 +6286,39 @@
         <v>56</v>
       </c>
       <c r="B295" t="str">
-        <v>Moor of Icirrus</v>
+        <v>Pokemon League</v>
       </c>
       <c r="C295" t="str">
         <v/>
       </c>
       <c r="D295" t="str">
-        <v>Ducklett</v>
+        <v/>
       </c>
       <c r="E295" t="str">
-        <v>76-77</v>
+        <v>63-65</v>
       </c>
       <c r="F295" t="str">
-        <v>33.33%</v>
+        <v/>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B296" t="str">
-        <v>Moor of Icirrus</v>
+        <v>Route 8</v>
       </c>
       <c r="C296" t="str">
         <v/>
       </c>
       <c r="D296" t="str">
-        <v>Toxicroak</v>
+        <v>Palpitoad</v>
       </c>
       <c r="E296" t="str">
-        <v>76-77</v>
+        <v>25-26</v>
       </c>
       <c r="F296" t="str">
-        <v>33.33%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="297">
@@ -6326,19 +6326,19 @@
         <v>57</v>
       </c>
       <c r="B297" t="str">
-        <v>Icirrus City</v>
+        <v>Route 8</v>
       </c>
       <c r="C297" t="str">
         <v/>
       </c>
       <c r="D297" t="str">
-        <v>Lapras</v>
+        <v>Stunfisk</v>
       </c>
       <c r="E297" t="str">
-        <v>88-89</v>
+        <v>25-26</v>
       </c>
       <c r="F297" t="str">
-        <v>33.34%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="298">
@@ -6346,19 +6346,19 @@
         <v>57</v>
       </c>
       <c r="B298" t="str">
-        <v>Icirrus City</v>
+        <v>Route 8</v>
       </c>
       <c r="C298" t="str">
         <v/>
       </c>
       <c r="D298" t="str">
-        <v>Tirtouga</v>
+        <v>Shellder</v>
       </c>
       <c r="E298" t="str">
-        <v>88-89</v>
+        <v>25-26</v>
       </c>
       <c r="F298" t="str">
-        <v>33.33%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="299">
@@ -6366,39 +6366,39 @@
         <v>57</v>
       </c>
       <c r="B299" t="str">
-        <v>Icirrus City</v>
+        <v>Route 8</v>
       </c>
       <c r="C299" t="str">
         <v/>
       </c>
       <c r="D299" t="str">
-        <v>Beheeyem</v>
+        <v>Croagunk</v>
       </c>
       <c r="E299" t="str">
-        <v>88-89</v>
+        <v>25-26</v>
       </c>
       <c r="F299" t="str">
-        <v>33.33%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="300">
       <c r="A300">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B300" t="str">
-        <v>Dragonspiral Tower</v>
+        <v>Route 8</v>
       </c>
       <c r="C300" t="str">
         <v/>
       </c>
       <c r="D300" t="str">
-        <v>Golett</v>
+        <v>Crobat</v>
       </c>
       <c r="E300" t="str">
-        <v>99-100</v>
+        <v>25-26</v>
       </c>
       <c r="F300" t="str">
-        <v>14.26%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="301">
@@ -6406,19 +6406,19 @@
         <v>58</v>
       </c>
       <c r="B301" t="str">
-        <v>Dragonspiral Tower</v>
+        <v>Moor of Icirrus</v>
       </c>
       <c r="C301" t="str">
         <v/>
       </c>
       <c r="D301" t="str">
-        <v>Druddigon</v>
+        <v>Shelmet</v>
       </c>
       <c r="E301" t="str">
-        <v>99-100</v>
+        <v>32-33</v>
       </c>
       <c r="F301" t="str">
-        <v>14.29%</v>
+        <v>33.34%</v>
       </c>
     </row>
     <row r="302">
@@ -6426,19 +6426,19 @@
         <v>58</v>
       </c>
       <c r="B302" t="str">
-        <v>Dragonspiral Tower</v>
+        <v>Moor of Icirrus</v>
       </c>
       <c r="C302" t="str">
         <v/>
       </c>
       <c r="D302" t="str">
-        <v>Mienfoo</v>
+        <v>Ducklett</v>
       </c>
       <c r="E302" t="str">
-        <v>99-100</v>
+        <v>32-33</v>
       </c>
       <c r="F302" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="303">
@@ -6446,159 +6446,159 @@
         <v>58</v>
       </c>
       <c r="B303" t="str">
-        <v>Dragonspiral Tower</v>
+        <v>Moor of Icirrus</v>
       </c>
       <c r="C303" t="str">
         <v/>
       </c>
       <c r="D303" t="str">
-        <v>Golbat</v>
+        <v>Toxicroak</v>
       </c>
       <c r="E303" t="str">
-        <v>99-100</v>
+        <v>32-33</v>
       </c>
       <c r="F303" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="304">
       <c r="A304">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B304" t="str">
-        <v>Dragonspiral Tower</v>
+        <v>Icirrus City</v>
       </c>
       <c r="C304" t="str">
         <v/>
       </c>
       <c r="D304" t="str">
-        <v>Fraxure</v>
+        <v>Lapras</v>
       </c>
       <c r="E304" t="str">
-        <v>99-100</v>
+        <v>39-40</v>
       </c>
       <c r="F304" t="str">
-        <v>14.29%</v>
+        <v>33.34%</v>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B305" t="str">
-        <v>Dragonspiral Tower</v>
+        <v>Icirrus City</v>
       </c>
       <c r="C305" t="str">
         <v/>
       </c>
       <c r="D305" t="str">
-        <v>Haxorus</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E305" t="str">
-        <v>99-100</v>
+        <v>39-40</v>
       </c>
       <c r="F305" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="306">
       <c r="A306">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B306" t="str">
-        <v>Dragonspiral Tower</v>
+        <v>Icirrus City</v>
       </c>
       <c r="C306" t="str">
         <v/>
       </c>
       <c r="D306" t="str">
-        <v>Beartic</v>
+        <v>Beheeyem</v>
       </c>
       <c r="E306" t="str">
-        <v>99-100</v>
+        <v>39-40</v>
       </c>
       <c r="F306" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="307">
       <c r="A307">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B307" t="str">
-        <v>Moor of Icirrus Depths</v>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="C307" t="str">
         <v/>
       </c>
       <c r="D307" t="str">
-        <v>Cobalion</v>
+        <v>Golett</v>
       </c>
       <c r="E307" t="str">
-        <v>110</v>
+        <v>46-47</v>
       </c>
       <c r="F307" t="str">
-        <v>25%</v>
+        <v>14.26%</v>
       </c>
     </row>
     <row r="308">
       <c r="A308">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B308" t="str">
-        <v>Moor of Icirrus Depths</v>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="C308" t="str">
         <v/>
       </c>
       <c r="D308" t="str">
-        <v>Terrakion</v>
+        <v>Druddigon</v>
       </c>
       <c r="E308" t="str">
-        <v>110</v>
+        <v>46-47</v>
       </c>
       <c r="F308" t="str">
-        <v>25%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="309">
       <c r="A309">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B309" t="str">
-        <v>Moor of Icirrus Depths</v>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="C309" t="str">
         <v/>
       </c>
       <c r="D309" t="str">
-        <v>Virizion</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E309" t="str">
-        <v>110</v>
+        <v>46-47</v>
       </c>
       <c r="F309" t="str">
-        <v>25%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="310">
       <c r="A310">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B310" t="str">
-        <v>Moor of Icirrus Depths</v>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="C310" t="str">
         <v/>
       </c>
       <c r="D310" t="str">
-        <v>Keldeo</v>
+        <v>Golbat</v>
       </c>
       <c r="E310" t="str">
-        <v>110</v>
+        <v>46-47</v>
       </c>
       <c r="F310" t="str">
-        <v>25%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="311">
@@ -6606,19 +6606,19 @@
         <v>60</v>
       </c>
       <c r="B311" t="str">
-        <v>Twist Mountain</v>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="C311" t="str">
         <v/>
       </c>
       <c r="D311" t="str">
-        <v>Boldore</v>
+        <v>Fraxure</v>
       </c>
       <c r="E311" t="str">
-        <v>65-66</v>
+        <v>46-47</v>
       </c>
       <c r="F311" t="str">
-        <v>12.5%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="312">
@@ -6626,19 +6626,19 @@
         <v>60</v>
       </c>
       <c r="B312" t="str">
-        <v>Twist Mountain</v>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="C312" t="str">
         <v/>
       </c>
       <c r="D312" t="str">
-        <v>Gurdurr</v>
+        <v>Haxorus</v>
       </c>
       <c r="E312" t="str">
-        <v>65-66</v>
+        <v>46-47</v>
       </c>
       <c r="F312" t="str">
-        <v>12.5%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="313">
@@ -6646,24 +6646,24 @@
         <v>60</v>
       </c>
       <c r="B313" t="str">
-        <v>Twist Mountain</v>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="C313" t="str">
         <v/>
       </c>
       <c r="D313" t="str">
-        <v>Cryogonal</v>
+        <v>Beartic</v>
       </c>
       <c r="E313" t="str">
-        <v>65-66</v>
+        <v>46-47</v>
       </c>
       <c r="F313" t="str">
-        <v>12.5%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B314" t="str">
         <v>Twist Mountain</v>
@@ -6672,10 +6672,10 @@
         <v/>
       </c>
       <c r="D314" t="str">
-        <v>Woobat</v>
+        <v>Boldore</v>
       </c>
       <c r="E314" t="str">
-        <v>65-66</v>
+        <v>53-54</v>
       </c>
       <c r="F314" t="str">
         <v>12.5%</v>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="315">
       <c r="A315">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B315" t="str">
         <v>Twist Mountain</v>
@@ -6692,10 +6692,10 @@
         <v/>
       </c>
       <c r="D315" t="str">
-        <v>Larvitar</v>
+        <v>Gurdurr</v>
       </c>
       <c r="E315" t="str">
-        <v>65-66</v>
+        <v>53-54</v>
       </c>
       <c r="F315" t="str">
         <v>12.5%</v>
@@ -6703,7 +6703,7 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B316" t="str">
         <v>Twist Mountain</v>
@@ -6712,10 +6712,10 @@
         <v/>
       </c>
       <c r="D316" t="str">
-        <v>Mamoswine</v>
+        <v>Cryogonal</v>
       </c>
       <c r="E316" t="str">
-        <v>65-66</v>
+        <v>53-54</v>
       </c>
       <c r="F316" t="str">
         <v>12.5%</v>
@@ -6723,7 +6723,7 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B317" t="str">
         <v>Twist Mountain</v>
@@ -6732,10 +6732,10 @@
         <v/>
       </c>
       <c r="D317" t="str">
-        <v>Vanillish</v>
+        <v>Woobat</v>
       </c>
       <c r="E317" t="str">
-        <v>65-66</v>
+        <v>53-54</v>
       </c>
       <c r="F317" t="str">
         <v>12.5%</v>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B318" t="str">
         <v>Twist Mountain</v>
@@ -6752,10 +6752,10 @@
         <v/>
       </c>
       <c r="D318" t="str">
-        <v>Vanilluxe</v>
+        <v>Larvitar</v>
       </c>
       <c r="E318" t="str">
-        <v>65-66</v>
+        <v>53-54</v>
       </c>
       <c r="F318" t="str">
         <v>12.5%</v>
@@ -6766,19 +6766,19 @@
         <v>61</v>
       </c>
       <c r="B319" t="str">
-        <v>Underground Ruins</v>
+        <v>Twist Mountain</v>
       </c>
       <c r="C319" t="str">
         <v/>
       </c>
       <c r="D319" t="str">
-        <v>Boldore</v>
+        <v>Mamoswine</v>
       </c>
       <c r="E319" t="str">
-        <v>71-72</v>
+        <v>53-54</v>
       </c>
       <c r="F319" t="str">
-        <v>11.12%</v>
+        <v>12.5%</v>
       </c>
     </row>
     <row r="320">
@@ -6786,19 +6786,19 @@
         <v>61</v>
       </c>
       <c r="B320" t="str">
-        <v>Underground Ruins</v>
+        <v>Twist Mountain</v>
       </c>
       <c r="C320" t="str">
         <v/>
       </c>
       <c r="D320" t="str">
-        <v>Nosepass</v>
+        <v>Vanillish</v>
       </c>
       <c r="E320" t="str">
-        <v>71-72</v>
+        <v>53-54</v>
       </c>
       <c r="F320" t="str">
-        <v>11.11%</v>
+        <v>12.5%</v>
       </c>
     </row>
     <row r="321">
@@ -6806,24 +6806,24 @@
         <v>61</v>
       </c>
       <c r="B321" t="str">
-        <v>Underground Ruins</v>
+        <v>Twist Mountain</v>
       </c>
       <c r="C321" t="str">
         <v/>
       </c>
       <c r="D321" t="str">
-        <v>Lairon</v>
+        <v>Vanilluxe</v>
       </c>
       <c r="E321" t="str">
-        <v>71-72</v>
+        <v>53-54</v>
       </c>
       <c r="F321" t="str">
-        <v>11.11%</v>
+        <v>12.5%</v>
       </c>
     </row>
     <row r="322">
       <c r="A322">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B322" t="str">
         <v>Underground Ruins</v>
@@ -6832,18 +6832,18 @@
         <v/>
       </c>
       <c r="D322" t="str">
-        <v>Woobat</v>
+        <v>Boldore</v>
       </c>
       <c r="E322" t="str">
-        <v>71-72</v>
+        <v>60</v>
       </c>
       <c r="F322" t="str">
-        <v>11.11%</v>
+        <v>11.12%</v>
       </c>
     </row>
     <row r="323">
       <c r="A323">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B323" t="str">
         <v>Underground Ruins</v>
@@ -6852,10 +6852,10 @@
         <v/>
       </c>
       <c r="D323" t="str">
-        <v>Durant</v>
+        <v>Nosepass</v>
       </c>
       <c r="E323" t="str">
-        <v>71-72</v>
+        <v>60</v>
       </c>
       <c r="F323" t="str">
         <v>11.11%</v>
@@ -6863,7 +6863,7 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B324" t="str">
         <v>Underground Ruins</v>
@@ -6872,10 +6872,10 @@
         <v/>
       </c>
       <c r="D324" t="str">
-        <v>Onix</v>
+        <v>Lairon</v>
       </c>
       <c r="E324" t="str">
-        <v>71-72</v>
+        <v>60</v>
       </c>
       <c r="F324" t="str">
         <v>11.11%</v>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B325" t="str">
         <v>Underground Ruins</v>
@@ -6892,10 +6892,10 @@
         <v/>
       </c>
       <c r="D325" t="str">
-        <v>Steelix</v>
+        <v>Woobat</v>
       </c>
       <c r="E325" t="str">
-        <v>71-72</v>
+        <v>60</v>
       </c>
       <c r="F325" t="str">
         <v>11.11%</v>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B326" t="str">
         <v>Underground Ruins</v>
@@ -6912,10 +6912,10 @@
         <v/>
       </c>
       <c r="D326" t="str">
-        <v>Aggron</v>
+        <v>Durant</v>
       </c>
       <c r="E326" t="str">
-        <v>71-72</v>
+        <v>60</v>
       </c>
       <c r="F326" t="str">
         <v>11.11%</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B327" t="str">
         <v>Underground Ruins</v>
@@ -6932,10 +6932,10 @@
         <v/>
       </c>
       <c r="D327" t="str">
-        <v>Probopass</v>
+        <v>Onix</v>
       </c>
       <c r="E327" t="str">
-        <v>71-72</v>
+        <v>60</v>
       </c>
       <c r="F327" t="str">
         <v>11.11%</v>
@@ -6946,19 +6946,19 @@
         <v>62</v>
       </c>
       <c r="B328" t="str">
-        <v>Route 15</v>
+        <v>Underground Ruins</v>
       </c>
       <c r="C328" t="str">
         <v/>
       </c>
       <c r="D328" t="str">
-        <v>Gligar</v>
+        <v>Steelix</v>
       </c>
       <c r="E328" t="str">
-        <v>77-78</v>
+        <v>60</v>
       </c>
       <c r="F328" t="str">
-        <v>16.65%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="329">
@@ -6966,19 +6966,19 @@
         <v>62</v>
       </c>
       <c r="B329" t="str">
-        <v>Route 15</v>
+        <v>Underground Ruins</v>
       </c>
       <c r="C329" t="str">
         <v/>
       </c>
       <c r="D329" t="str">
-        <v>Pupitar</v>
+        <v>Aggron</v>
       </c>
       <c r="E329" t="str">
-        <v>77-78</v>
+        <v>60</v>
       </c>
       <c r="F329" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="330">
@@ -6986,24 +6986,24 @@
         <v>62</v>
       </c>
       <c r="B330" t="str">
-        <v>Route 15</v>
+        <v>Underground Ruins</v>
       </c>
       <c r="C330" t="str">
         <v/>
       </c>
       <c r="D330" t="str">
-        <v>Scraggy</v>
+        <v>Probopass</v>
       </c>
       <c r="E330" t="str">
-        <v>77-78</v>
+        <v>60</v>
       </c>
       <c r="F330" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="331">
       <c r="A331">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B331" t="str">
         <v>Route 15</v>
@@ -7012,18 +7012,18 @@
         <v/>
       </c>
       <c r="D331" t="str">
-        <v>Foongus</v>
+        <v>Gligar</v>
       </c>
       <c r="E331" t="str">
-        <v>77-78</v>
+        <v>35-36</v>
       </c>
       <c r="F331" t="str">
-        <v>16.67%</v>
+        <v>16.65%</v>
       </c>
     </row>
     <row r="332">
       <c r="A332">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B332" t="str">
         <v>Route 15</v>
@@ -7032,10 +7032,10 @@
         <v/>
       </c>
       <c r="D332" t="str">
-        <v>Koffing</v>
+        <v>Pupitar</v>
       </c>
       <c r="E332" t="str">
-        <v>77-78</v>
+        <v>35-36</v>
       </c>
       <c r="F332" t="str">
         <v>16.67%</v>
@@ -7043,7 +7043,7 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B333" t="str">
         <v>Route 15</v>
@@ -7052,10 +7052,10 @@
         <v/>
       </c>
       <c r="D333" t="str">
-        <v>Tyranitar</v>
+        <v>Scraggy</v>
       </c>
       <c r="E333" t="str">
-        <v>77-78</v>
+        <v>35-36</v>
       </c>
       <c r="F333" t="str">
         <v>16.67%</v>
@@ -7066,19 +7066,19 @@
         <v>63</v>
       </c>
       <c r="B334" t="str">
-        <v>Route 16</v>
+        <v>Route 15</v>
       </c>
       <c r="C334" t="str">
         <v/>
       </c>
       <c r="D334" t="str">
-        <v>Gothitelle</v>
+        <v>Foongus</v>
       </c>
       <c r="E334" t="str">
-        <v>83-84</v>
+        <v>35-36</v>
       </c>
       <c r="F334" t="str">
-        <v>16.65%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="335">
@@ -7086,16 +7086,16 @@
         <v>63</v>
       </c>
       <c r="B335" t="str">
-        <v>Route 16</v>
+        <v>Route 15</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335" t="str">
-        <v>Reuniclus</v>
+        <v>Koffing</v>
       </c>
       <c r="E335" t="str">
-        <v>83-84</v>
+        <v>35-36</v>
       </c>
       <c r="F335" t="str">
         <v>16.67%</v>
@@ -7106,16 +7106,16 @@
         <v>63</v>
       </c>
       <c r="B336" t="str">
-        <v>Route 16</v>
+        <v>Route 15</v>
       </c>
       <c r="C336" t="str">
         <v/>
       </c>
       <c r="D336" t="str">
-        <v>Trubbish</v>
+        <v>Tyranitar</v>
       </c>
       <c r="E336" t="str">
-        <v>83-84</v>
+        <v>35-36</v>
       </c>
       <c r="F336" t="str">
         <v>16.67%</v>
@@ -7123,62 +7123,62 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B337" t="str">
-        <v>Route 16</v>
+        <v>Striaton City</v>
       </c>
       <c r="C337" t="str">
         <v/>
       </c>
       <c r="D337" t="str">
-        <v>Foongus</v>
+        <v>Panpour</v>
       </c>
       <c r="E337" t="str">
-        <v>83-84</v>
+        <v>44-45</v>
       </c>
       <c r="F337" t="str">
-        <v>16.67%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="338">
       <c r="A338">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B338" t="str">
-        <v>Route 16</v>
+        <v>Striaton City</v>
       </c>
       <c r="C338" t="str">
         <v/>
       </c>
       <c r="D338" t="str">
-        <v>Emolga</v>
+        <v>Pansear</v>
       </c>
       <c r="E338" t="str">
-        <v>83-84</v>
+        <v>44-45</v>
       </c>
       <c r="F338" t="str">
-        <v>16.67%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="339">
       <c r="A339">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B339" t="str">
-        <v>Route 16</v>
+        <v>Striaton City</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339" t="str">
-        <v>Joltik</v>
+        <v>Jigglypuff</v>
       </c>
       <c r="E339" t="str">
-        <v>83-84</v>
+        <v>44-45</v>
       </c>
       <c r="F339" t="str">
-        <v>16.67%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="340">
@@ -7192,10 +7192,10 @@
         <v/>
       </c>
       <c r="D340" t="str">
-        <v>Panpour</v>
+        <v>Wigglytuff</v>
       </c>
       <c r="E340" t="str">
-        <v>89-90</v>
+        <v>44-45</v>
       </c>
       <c r="F340" t="str">
         <v>25%</v>
@@ -7203,122 +7203,122 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B341" t="str">
-        <v>Striaton City</v>
+        <v>Dreamyard</v>
       </c>
       <c r="C341" t="str">
         <v/>
       </c>
       <c r="D341" t="str">
-        <v>Pansear</v>
+        <v>Munna</v>
       </c>
       <c r="E341" t="str">
-        <v>89-90</v>
+        <v>53-54</v>
       </c>
       <c r="F341" t="str">
-        <v>25%</v>
+        <v>33.34%</v>
       </c>
     </row>
     <row r="342">
       <c r="A342">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B342" t="str">
-        <v>Striaton City</v>
+        <v>Dreamyard</v>
       </c>
       <c r="C342" t="str">
         <v/>
       </c>
       <c r="D342" t="str">
-        <v>Jigglypuff</v>
+        <v>Rufflet</v>
       </c>
       <c r="E342" t="str">
-        <v>89-90</v>
+        <v>53-54</v>
       </c>
       <c r="F342" t="str">
-        <v>25%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="343">
       <c r="A343">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B343" t="str">
-        <v>Striaton City</v>
+        <v>Dreamyard</v>
       </c>
       <c r="C343" t="str">
         <v/>
       </c>
       <c r="D343" t="str">
-        <v>Wigglytuff</v>
+        <v>Musharna</v>
       </c>
       <c r="E343" t="str">
-        <v>89-90</v>
+        <v>53-54</v>
       </c>
       <c r="F343" t="str">
-        <v>25%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="344">
       <c r="A344">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B344" t="str">
-        <v>Dreamyard</v>
+        <v>Route 18</v>
       </c>
       <c r="C344" t="str">
         <v/>
       </c>
       <c r="D344" t="str">
-        <v>Munna</v>
+        <v>Scraggy</v>
       </c>
       <c r="E344" t="str">
-        <v>95</v>
+        <v>61-62</v>
       </c>
       <c r="F344" t="str">
-        <v>33.34%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="345">
       <c r="A345">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B345" t="str">
-        <v>Dreamyard</v>
+        <v>Route 18</v>
       </c>
       <c r="C345" t="str">
         <v/>
       </c>
       <c r="D345" t="str">
-        <v>Rufflet</v>
+        <v>Crustle</v>
       </c>
       <c r="E345" t="str">
-        <v>95</v>
+        <v>61-62</v>
       </c>
       <c r="F345" t="str">
-        <v>33.33%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="346">
       <c r="A346">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B346" t="str">
-        <v>Dreamyard</v>
+        <v>Route 18</v>
       </c>
       <c r="C346" t="str">
         <v/>
       </c>
       <c r="D346" t="str">
-        <v>Musharna</v>
+        <v>Carnivine</v>
       </c>
       <c r="E346" t="str">
-        <v>95</v>
+        <v>61-62</v>
       </c>
       <c r="F346" t="str">
-        <v>33.33%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="347">
@@ -7332,10 +7332,10 @@
         <v/>
       </c>
       <c r="D347" t="str">
-        <v>Scraggy</v>
+        <v>Drifblim</v>
       </c>
       <c r="E347" t="str">
-        <v>65-66</v>
+        <v>61-62</v>
       </c>
       <c r="F347" t="str">
         <v>20%</v>
@@ -7352,10 +7352,10 @@
         <v/>
       </c>
       <c r="D348" t="str">
-        <v>Crustle</v>
+        <v>Scrafty</v>
       </c>
       <c r="E348" t="str">
-        <v>65-66</v>
+        <v>61-62</v>
       </c>
       <c r="F348" t="str">
         <v>20%</v>
@@ -7363,99 +7363,99 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B349" t="str">
-        <v>Route 18</v>
+        <v>Route 17</v>
       </c>
       <c r="C349" t="str">
         <v/>
       </c>
       <c r="D349" t="str">
-        <v>Carnivine</v>
+        <v>Frillish</v>
       </c>
       <c r="E349" t="str">
-        <v>65-66</v>
+        <v>70</v>
       </c>
       <c r="F349" t="str">
-        <v>20%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="350">
       <c r="A350">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B350" t="str">
-        <v>Route 18</v>
+        <v>Route 17</v>
       </c>
       <c r="C350" t="str">
         <v/>
       </c>
       <c r="D350" t="str">
-        <v>Drifblim</v>
+        <v>Alomomola</v>
       </c>
       <c r="E350" t="str">
-        <v>65-66</v>
+        <v>70</v>
       </c>
       <c r="F350" t="str">
-        <v>20%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="351">
       <c r="A351">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B351" t="str">
-        <v>Route 18</v>
+        <v>Route 1</v>
       </c>
       <c r="C351" t="str">
         <v/>
       </c>
       <c r="D351" t="str">
-        <v>Scrafty</v>
+        <v>Tepig</v>
       </c>
       <c r="E351" t="str">
         <v>65-66</v>
       </c>
       <c r="F351" t="str">
-        <v>20%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="352">
       <c r="A352">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B352" t="str">
-        <v>P2 Laboratory</v>
+        <v>Route 1</v>
       </c>
       <c r="C352" t="str">
         <v/>
       </c>
       <c r="D352" t="str">
-        <v>Beldum</v>
+        <v>Oshawott</v>
       </c>
       <c r="E352" t="str">
-        <v>74-75</v>
+        <v>65-66</v>
       </c>
       <c r="F352" t="str">
-        <v>25%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="353">
       <c r="A353">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B353" t="str">
-        <v>P2 Laboratory</v>
+        <v>Nuvema Town</v>
       </c>
       <c r="C353" t="str">
         <v/>
       </c>
       <c r="D353" t="str">
-        <v>Pawniard</v>
+        <v>Cleffa</v>
       </c>
       <c r="E353" t="str">
-        <v>74-75</v>
+        <v>76-77</v>
       </c>
       <c r="F353" t="str">
         <v>25%</v>
@@ -7463,19 +7463,19 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B354" t="str">
-        <v>P2 Laboratory</v>
+        <v>Nuvema Town</v>
       </c>
       <c r="C354" t="str">
         <v/>
       </c>
       <c r="D354" t="str">
-        <v>Magnezone</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E354" t="str">
-        <v>74-75</v>
+        <v>76-77</v>
       </c>
       <c r="F354" t="str">
         <v>25%</v>
@@ -7483,19 +7483,19 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B355" t="str">
-        <v>P2 Laboratory</v>
+        <v>Nuvema Town</v>
       </c>
       <c r="C355" t="str">
         <v/>
       </c>
       <c r="D355" t="str">
-        <v>Klinklang</v>
+        <v>Ampharos</v>
       </c>
       <c r="E355" t="str">
-        <v>74-75</v>
+        <v>76-77</v>
       </c>
       <c r="F355" t="str">
         <v>25%</v>
@@ -7503,79 +7503,79 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B356" t="str">
-        <v>Route 17</v>
+        <v>Nuvema Town</v>
       </c>
       <c r="C356" t="str">
         <v/>
       </c>
       <c r="D356" t="str">
-        <v>Frillish</v>
+        <v>Flaaffy</v>
       </c>
       <c r="E356" t="str">
-        <v>83-84</v>
+        <v>76-77</v>
       </c>
       <c r="F356" t="str">
-        <v>50%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="357">
       <c r="A357">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B357" t="str">
-        <v>Route 17</v>
+        <v>Route 2</v>
       </c>
       <c r="C357" t="str">
         <v/>
       </c>
       <c r="D357" t="str">
-        <v>Alomomola</v>
+        <v>Blitzle</v>
       </c>
       <c r="E357" t="str">
-        <v>83-84</v>
+        <v>88-89</v>
       </c>
       <c r="F357" t="str">
-        <v>50%</v>
+        <v>16.65%</v>
       </c>
     </row>
     <row r="358">
       <c r="A358">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B358" t="str">
-        <v>Cave of Being</v>
+        <v>Route 2</v>
       </c>
       <c r="C358" t="str">
         <v/>
       </c>
       <c r="D358" t="str">
-        <v>Roggenrola</v>
+        <v>Spoink</v>
       </c>
       <c r="E358" t="str">
-        <v>92-93</v>
+        <v>88-89</v>
       </c>
       <c r="F358" t="str">
-        <v>16.65%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="359">
       <c r="A359">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B359" t="str">
-        <v>Cave of Being</v>
+        <v>Route 2</v>
       </c>
       <c r="C359" t="str">
         <v/>
       </c>
       <c r="D359" t="str">
-        <v>Axew</v>
+        <v>Lickitung</v>
       </c>
       <c r="E359" t="str">
-        <v>92-93</v>
+        <v>88-89</v>
       </c>
       <c r="F359" t="str">
         <v>16.67%</v>
@@ -7583,19 +7583,19 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B360" t="str">
-        <v>Cave of Being</v>
+        <v>Route 2</v>
       </c>
       <c r="C360" t="str">
         <v/>
       </c>
       <c r="D360" t="str">
-        <v>Lucario</v>
+        <v>Lickilicky</v>
       </c>
       <c r="E360" t="str">
-        <v>92-93</v>
+        <v>88-89</v>
       </c>
       <c r="F360" t="str">
         <v>16.67%</v>
@@ -7603,19 +7603,19 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B361" t="str">
-        <v>Cave of Being</v>
+        <v>Route 2</v>
       </c>
       <c r="C361" t="str">
         <v/>
       </c>
       <c r="D361" t="str">
-        <v>Simisage</v>
+        <v>Vigoroth</v>
       </c>
       <c r="E361" t="str">
-        <v>92-93</v>
+        <v>88-89</v>
       </c>
       <c r="F361" t="str">
         <v>16.67%</v>
@@ -7623,19 +7623,19 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B362" t="str">
-        <v>Cave of Being</v>
+        <v>Route 2</v>
       </c>
       <c r="C362" t="str">
         <v/>
       </c>
       <c r="D362" t="str">
-        <v>Simisear</v>
+        <v>Slaking</v>
       </c>
       <c r="E362" t="str">
-        <v>92-93</v>
+        <v>88-89</v>
       </c>
       <c r="F362" t="str">
         <v>16.67%</v>
@@ -7643,162 +7643,162 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B363" t="str">
-        <v>Cave of Being</v>
+        <v>Route 3</v>
       </c>
       <c r="C363" t="str">
         <v/>
       </c>
       <c r="D363" t="str">
-        <v>Simipour</v>
+        <v>Throh</v>
       </c>
       <c r="E363" t="str">
-        <v>92-93</v>
+        <v>99-100</v>
       </c>
       <c r="F363" t="str">
-        <v>16.67%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B364" t="str">
-        <v>Nature Sanctuary</v>
+        <v>Route 3</v>
       </c>
       <c r="C364" t="str">
         <v/>
       </c>
       <c r="D364" t="str">
-        <v>Yanma</v>
+        <v>Sawk</v>
       </c>
       <c r="E364" t="str">
-        <v>101-102</v>
+        <v>99-100</v>
       </c>
       <c r="F364" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="365">
       <c r="A365">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B365" t="str">
-        <v>Nature Sanctuary</v>
+        <v>Route 3</v>
       </c>
       <c r="C365" t="str">
         <v/>
       </c>
       <c r="D365" t="str">
-        <v>Zorua</v>
+        <v>Conkeldurr</v>
       </c>
       <c r="E365" t="str">
-        <v>101-102</v>
+        <v>99-100</v>
       </c>
       <c r="F365" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="366">
       <c r="A366">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B366" t="str">
-        <v>Nature Sanctuary</v>
+        <v>Route 3</v>
       </c>
       <c r="C366" t="str">
         <v/>
       </c>
       <c r="D366" t="str">
-        <v>Arcanine</v>
+        <v>Electabuzz</v>
       </c>
       <c r="E366" t="str">
-        <v>101-102</v>
+        <v>99-100</v>
       </c>
       <c r="F366" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B367" t="str">
-        <v>Nature Sanctuary</v>
+        <v>Route 3</v>
       </c>
       <c r="C367" t="str">
         <v/>
       </c>
       <c r="D367" t="str">
-        <v>Ninetales</v>
+        <v>Electivire</v>
       </c>
       <c r="E367" t="str">
-        <v>101-102</v>
+        <v>99-100</v>
       </c>
       <c r="F367" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B368" t="str">
-        <v>Liberty Garden</v>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="C368" t="str">
         <v/>
       </c>
       <c r="D368" t="str">
-        <v>Victini</v>
+        <v>Cobalion</v>
       </c>
       <c r="E368" t="str">
         <v>110</v>
       </c>
       <c r="F368" t="str">
-        <v>33.34%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B369" t="str">
-        <v>Liberty Garden</v>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="C369" t="str">
         <v/>
       </c>
       <c r="D369" t="str">
-        <v>Meloetta</v>
+        <v>Terrakion</v>
       </c>
       <c r="E369" t="str">
         <v>110</v>
       </c>
       <c r="F369" t="str">
-        <v>33.33%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B370" t="str">
-        <v>Liberty Garden</v>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="C370" t="str">
         <v/>
       </c>
       <c r="D370" t="str">
-        <v>Genesect</v>
+        <v>Virizion</v>
       </c>
       <c r="E370" t="str">
         <v>110</v>
       </c>
       <c r="F370" t="str">
-        <v>33.33%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="371">
@@ -7806,56 +7806,56 @@
         <v>72</v>
       </c>
       <c r="B371" t="str">
-        <v>Route 1</v>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="C371" t="str">
         <v/>
       </c>
       <c r="D371" t="str">
-        <v>Tepig</v>
+        <v>Keldeo</v>
       </c>
       <c r="E371" t="str">
-        <v>65-66</v>
+        <v>110</v>
       </c>
       <c r="F371" t="str">
-        <v>50%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B372" t="str">
-        <v>Route 1</v>
+        <v>Daycare</v>
       </c>
       <c r="C372" t="str">
         <v/>
       </c>
       <c r="D372" t="str">
-        <v>Oshawott</v>
+        <v/>
       </c>
       <c r="E372" t="str">
-        <v>65-66</v>
+        <v/>
       </c>
       <c r="F372" t="str">
-        <v>50%</v>
+        <v/>
       </c>
     </row>
     <row r="373">
       <c r="A373">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B373" t="str">
-        <v>Nuvema Town</v>
+        <v>Nacrene City</v>
       </c>
       <c r="C373" t="str">
         <v/>
       </c>
       <c r="D373" t="str">
-        <v>Cleffa</v>
+        <v>Tympole</v>
       </c>
       <c r="E373" t="str">
-        <v>69-70</v>
+        <v>76-77</v>
       </c>
       <c r="F373" t="str">
         <v>25%</v>
@@ -7863,19 +7863,19 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B374" t="str">
-        <v>Nuvema Town</v>
+        <v>Nacrene City</v>
       </c>
       <c r="C374" t="str">
         <v/>
       </c>
       <c r="D374" t="str">
-        <v>Igglybuff</v>
+        <v>Budew</v>
       </c>
       <c r="E374" t="str">
-        <v>69-70</v>
+        <v>76-77</v>
       </c>
       <c r="F374" t="str">
         <v>25%</v>
@@ -7883,19 +7883,19 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B375" t="str">
-        <v>Nuvema Town</v>
+        <v>Nacrene City</v>
       </c>
       <c r="C375" t="str">
         <v/>
       </c>
       <c r="D375" t="str">
-        <v>Ampharos</v>
+        <v>Herdier</v>
       </c>
       <c r="E375" t="str">
-        <v>69-70</v>
+        <v>76-77</v>
       </c>
       <c r="F375" t="str">
         <v>25%</v>
@@ -7903,19 +7903,19 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B376" t="str">
-        <v>Nuvema Town</v>
+        <v>Nacrene City</v>
       </c>
       <c r="C376" t="str">
         <v/>
       </c>
       <c r="D376" t="str">
-        <v>Flaaffy</v>
+        <v>Stoutland</v>
       </c>
       <c r="E376" t="str">
-        <v>69-70</v>
+        <v>76-77</v>
       </c>
       <c r="F376" t="str">
         <v>25%</v>
@@ -7923,119 +7923,119 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B377" t="str">
-        <v>Route 2</v>
+        <v>Pinwheel Forest</v>
       </c>
       <c r="C377" t="str">
         <v/>
       </c>
       <c r="D377" t="str">
-        <v>Blitzle</v>
+        <v>Snivy</v>
       </c>
       <c r="E377" t="str">
-        <v>74-75</v>
+        <v>88-89</v>
       </c>
       <c r="F377" t="str">
-        <v>16.65%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B378" t="str">
-        <v>Route 2</v>
+        <v>Pinwheel Forest</v>
       </c>
       <c r="C378" t="str">
         <v/>
       </c>
       <c r="D378" t="str">
-        <v>Spoink</v>
+        <v>Pansage</v>
       </c>
       <c r="E378" t="str">
-        <v>74-75</v>
+        <v>88-89</v>
       </c>
       <c r="F378" t="str">
-        <v>16.67%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B379" t="str">
-        <v>Route 2</v>
+        <v>Pinwheel Forest</v>
       </c>
       <c r="C379" t="str">
         <v/>
       </c>
       <c r="D379" t="str">
-        <v>Lickitung</v>
+        <v>Yanmega</v>
       </c>
       <c r="E379" t="str">
-        <v>74-75</v>
+        <v>88-89</v>
       </c>
       <c r="F379" t="str">
-        <v>16.67%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B380" t="str">
-        <v>Route 2</v>
+        <v>Pinwheel Forest</v>
       </c>
       <c r="C380" t="str">
         <v/>
       </c>
       <c r="D380" t="str">
-        <v>Lickilicky</v>
+        <v>Tangrowth</v>
       </c>
       <c r="E380" t="str">
-        <v>74-75</v>
+        <v>88-89</v>
       </c>
       <c r="F380" t="str">
-        <v>16.67%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B381" t="str">
-        <v>Route 2</v>
+        <v>Cave of Being</v>
       </c>
       <c r="C381" t="str">
         <v/>
       </c>
       <c r="D381" t="str">
-        <v>Vigoroth</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E381" t="str">
-        <v>74-75</v>
+        <v>99-100</v>
       </c>
       <c r="F381" t="str">
-        <v>16.67%</v>
+        <v>16.65%</v>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B382" t="str">
-        <v>Route 2</v>
+        <v>Cave of Being</v>
       </c>
       <c r="C382" t="str">
         <v/>
       </c>
       <c r="D382" t="str">
-        <v>Slaking</v>
+        <v>Axew</v>
       </c>
       <c r="E382" t="str">
-        <v>74-75</v>
+        <v>99-100</v>
       </c>
       <c r="F382" t="str">
         <v>16.67%</v>
@@ -8043,122 +8043,122 @@
     </row>
     <row r="383">
       <c r="A383">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B383" t="str">
-        <v>Route 3</v>
+        <v>Cave of Being</v>
       </c>
       <c r="C383" t="str">
         <v/>
       </c>
       <c r="D383" t="str">
-        <v>Throh</v>
+        <v>Lucario</v>
       </c>
       <c r="E383" t="str">
-        <v>78-79</v>
+        <v>99-100</v>
       </c>
       <c r="F383" t="str">
-        <v>20%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B384" t="str">
-        <v>Route 3</v>
+        <v>Cave of Being</v>
       </c>
       <c r="C384" t="str">
         <v/>
       </c>
       <c r="D384" t="str">
-        <v>Sawk</v>
+        <v>Simisage</v>
       </c>
       <c r="E384" t="str">
-        <v>78-79</v>
+        <v>99-100</v>
       </c>
       <c r="F384" t="str">
-        <v>20%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B385" t="str">
-        <v>Route 3</v>
+        <v>Cave of Being</v>
       </c>
       <c r="C385" t="str">
         <v/>
       </c>
       <c r="D385" t="str">
-        <v>Conkeldurr</v>
+        <v>Simisear</v>
       </c>
       <c r="E385" t="str">
-        <v>78-79</v>
+        <v>99-100</v>
       </c>
       <c r="F385" t="str">
-        <v>20%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B386" t="str">
-        <v>Route 3</v>
+        <v>Cave of Being</v>
       </c>
       <c r="C386" t="str">
         <v/>
       </c>
       <c r="D386" t="str">
-        <v>Electabuzz</v>
+        <v>Simipour</v>
       </c>
       <c r="E386" t="str">
-        <v>78-79</v>
+        <v>99-100</v>
       </c>
       <c r="F386" t="str">
-        <v>20%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B387" t="str">
-        <v>Route 3</v>
+        <v>Liberty Garden</v>
       </c>
       <c r="C387" t="str">
         <v/>
       </c>
       <c r="D387" t="str">
-        <v>Electivire</v>
+        <v>Victini</v>
       </c>
       <c r="E387" t="str">
-        <v>78-79</v>
+        <v>110</v>
       </c>
       <c r="F387" t="str">
-        <v>20%</v>
+        <v>33.34%</v>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B388" t="str">
-        <v>Daycare</v>
+        <v>Liberty Garden</v>
       </c>
       <c r="C388" t="str">
         <v/>
       </c>
       <c r="D388" t="str">
-        <v/>
+        <v>Meloetta</v>
       </c>
       <c r="E388" t="str">
-        <v/>
+        <v>110</v>
       </c>
       <c r="F388" t="str">
-        <v/>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="389">
@@ -8166,79 +8166,79 @@
         <v>77</v>
       </c>
       <c r="B389" t="str">
-        <v>Nacrene City</v>
+        <v>Liberty Garden</v>
       </c>
       <c r="C389" t="str">
         <v/>
       </c>
       <c r="D389" t="str">
-        <v>Tympole</v>
+        <v>Genesect</v>
       </c>
       <c r="E389" t="str">
-        <v>86-87</v>
+        <v>110</v>
       </c>
       <c r="F389" t="str">
-        <v>25%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B390" t="str">
-        <v>Nacrene City</v>
+        <v>Route 10</v>
       </c>
       <c r="C390" t="str">
         <v/>
       </c>
       <c r="D390" t="str">
-        <v>Budew</v>
+        <v>Bouffalant</v>
       </c>
       <c r="E390" t="str">
-        <v>86-87</v>
+        <v>65-66</v>
       </c>
       <c r="F390" t="str">
-        <v>25%</v>
+        <v>16.65%</v>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B391" t="str">
-        <v>Nacrene City</v>
+        <v>Route 10</v>
       </c>
       <c r="C391" t="str">
         <v/>
       </c>
       <c r="D391" t="str">
-        <v>Herdier</v>
+        <v>Braviary</v>
       </c>
       <c r="E391" t="str">
-        <v>86-87</v>
+        <v>65-66</v>
       </c>
       <c r="F391" t="str">
-        <v>25%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B392" t="str">
-        <v>Nacrene City</v>
+        <v>Route 10</v>
       </c>
       <c r="C392" t="str">
         <v/>
       </c>
       <c r="D392" t="str">
-        <v>Stoutland</v>
+        <v>Mandibuzz</v>
       </c>
       <c r="E392" t="str">
-        <v>86-87</v>
+        <v>65-66</v>
       </c>
       <c r="F392" t="str">
-        <v>25%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="393">
@@ -8246,19 +8246,19 @@
         <v>78</v>
       </c>
       <c r="B393" t="str">
-        <v>Pinwheel Forest</v>
+        <v>Route 10</v>
       </c>
       <c r="C393" t="str">
         <v/>
       </c>
       <c r="D393" t="str">
-        <v>Snivy</v>
+        <v>Amoonguss</v>
       </c>
       <c r="E393" t="str">
-        <v>91-92</v>
+        <v>65-66</v>
       </c>
       <c r="F393" t="str">
-        <v>25%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="394">
@@ -8266,19 +8266,19 @@
         <v>78</v>
       </c>
       <c r="B394" t="str">
-        <v>Pinwheel Forest</v>
+        <v>Route 10</v>
       </c>
       <c r="C394" t="str">
         <v/>
       </c>
       <c r="D394" t="str">
-        <v>Pansage</v>
+        <v>Eelektrik</v>
       </c>
       <c r="E394" t="str">
-        <v>91-92</v>
+        <v>65-66</v>
       </c>
       <c r="F394" t="str">
-        <v>25%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="395">
@@ -8286,36 +8286,36 @@
         <v>78</v>
       </c>
       <c r="B395" t="str">
-        <v>Pinwheel Forest</v>
+        <v>Route 10</v>
       </c>
       <c r="C395" t="str">
         <v/>
       </c>
       <c r="D395" t="str">
-        <v>Yanmega</v>
+        <v>Vullaby</v>
       </c>
       <c r="E395" t="str">
-        <v>91-92</v>
+        <v>65-66</v>
       </c>
       <c r="F395" t="str">
-        <v>25%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B396" t="str">
-        <v>Pinwheel Forest</v>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="C396" t="str">
         <v/>
       </c>
       <c r="D396" t="str">
-        <v>Tangrowth</v>
+        <v>Yanma</v>
       </c>
       <c r="E396" t="str">
-        <v>91-92</v>
+        <v>76-77</v>
       </c>
       <c r="F396" t="str">
         <v>25%</v>
@@ -8326,19 +8326,19 @@
         <v>79</v>
       </c>
       <c r="B397" t="str">
-        <v>Wellspring Cave</v>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="C397" t="str">
         <v/>
       </c>
       <c r="D397" t="str">
-        <v>Grimer</v>
+        <v>Zorua</v>
       </c>
       <c r="E397" t="str">
-        <v>95</v>
+        <v>76-77</v>
       </c>
       <c r="F397" t="str">
-        <v>33.34%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="398">
@@ -8346,19 +8346,19 @@
         <v>79</v>
       </c>
       <c r="B398" t="str">
-        <v>Wellspring Cave</v>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="C398" t="str">
         <v/>
       </c>
       <c r="D398" t="str">
-        <v>Bronzor</v>
+        <v>Arcanine</v>
       </c>
       <c r="E398" t="str">
-        <v>95</v>
+        <v>76-77</v>
       </c>
       <c r="F398" t="str">
-        <v>33.33%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="399">
@@ -8366,19 +8366,19 @@
         <v>79</v>
       </c>
       <c r="B399" t="str">
-        <v>Wellspring Cave</v>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="C399" t="str">
         <v/>
       </c>
       <c r="D399" t="str">
-        <v>Weezing</v>
+        <v>Ninetales</v>
       </c>
       <c r="E399" t="str">
-        <v>95</v>
+        <v>76-77</v>
       </c>
       <c r="F399" t="str">
-        <v>33.33%</v>
+        <v>25%</v>
       </c>
     </row>
     <row r="400">
@@ -8386,19 +8386,19 @@
         <v>80</v>
       </c>
       <c r="B400" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Route 24</v>
       </c>
       <c r="C400" t="str">
         <v/>
       </c>
       <c r="D400" t="str">
-        <v>Remoraid</v>
+        <v>Cryogonal</v>
       </c>
       <c r="E400" t="str">
-        <v>65-66</v>
+        <v>88-89</v>
       </c>
       <c r="F400" t="str">
-        <v>12.5%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="401">
@@ -8406,391 +8406,191 @@
         <v>80</v>
       </c>
       <c r="B401" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Route 24</v>
       </c>
       <c r="C401" t="str">
         <v/>
       </c>
       <c r="D401" t="str">
-        <v>Carvanha</v>
+        <v>Beartic</v>
       </c>
       <c r="E401" t="str">
-        <v>65-66</v>
+        <v>88-89</v>
       </c>
       <c r="F401" t="str">
-        <v>12.5%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B402" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Route 25</v>
       </c>
       <c r="C402" t="str">
         <v/>
       </c>
       <c r="D402" t="str">
-        <v>Chinchou</v>
+        <v>Stunfisk</v>
       </c>
       <c r="E402" t="str">
-        <v>65-66</v>
+        <v>99-100</v>
       </c>
       <c r="F402" t="str">
-        <v>12.5%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B403" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Route 25</v>
       </c>
       <c r="C403" t="str">
         <v/>
       </c>
       <c r="D403" t="str">
-        <v>Finneon</v>
+        <v>Bouffalant</v>
       </c>
       <c r="E403" t="str">
-        <v>65-66</v>
+        <v>99-100</v>
       </c>
       <c r="F403" t="str">
-        <v>12.5%</v>
+        <v>50%</v>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B404" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Abundant Shrine Depths</v>
       </c>
       <c r="C404" t="str">
         <v/>
       </c>
       <c r="D404" t="str">
-        <v>Goldeen</v>
+        <v>Landorus</v>
       </c>
       <c r="E404" t="str">
-        <v>65-66</v>
+        <v>110</v>
       </c>
       <c r="F404" t="str">
-        <v>12.5%</v>
+        <v>33.34%</v>
       </c>
     </row>
     <row r="405">
       <c r="A405">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B405" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Abundant Shrine Depths</v>
       </c>
       <c r="C405" t="str">
         <v/>
       </c>
       <c r="D405" t="str">
-        <v>Luvdisc</v>
+        <v>Thundurus</v>
       </c>
       <c r="E405" t="str">
-        <v>65-66</v>
+        <v>110</v>
       </c>
       <c r="F405" t="str">
-        <v>12.5%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B406" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Abundant Shrine Depths</v>
       </c>
       <c r="C406" t="str">
         <v/>
       </c>
       <c r="D406" t="str">
-        <v>Shellder</v>
+        <v>Tornadus</v>
       </c>
       <c r="E406" t="str">
-        <v>65-66</v>
+        <v>110</v>
       </c>
       <c r="F406" t="str">
-        <v>12.5%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B407" t="str">
-        <v>Driftveil Drawbridge</v>
+        <v>Dragonspire Clouds</v>
       </c>
       <c r="C407" t="str">
         <v/>
       </c>
       <c r="D407" t="str">
-        <v>Swanna</v>
+        <v>Kyurem</v>
       </c>
       <c r="E407" t="str">
-        <v>65-66</v>
+        <v>120-121</v>
       </c>
       <c r="F407" t="str">
-        <v>12.5%</v>
+        <v>33.34%</v>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B408" t="str">
-        <v>Route 10</v>
+        <v>Dragonspire Clouds</v>
       </c>
       <c r="C408" t="str">
         <v/>
       </c>
       <c r="D408" t="str">
-        <v>Bouffalant</v>
+        <v>Reshiram</v>
       </c>
       <c r="E408" t="str">
-        <v>88-89</v>
+        <v>120-121</v>
       </c>
       <c r="F408" t="str">
-        <v>16.65%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B409" t="str">
-        <v>Route 10</v>
+        <v>Dragonspire Clouds</v>
       </c>
       <c r="C409" t="str">
         <v/>
       </c>
       <c r="D409" t="str">
-        <v>Braviary</v>
+        <v>Zekrom</v>
       </c>
       <c r="E409" t="str">
-        <v>88-89</v>
+        <v>120-121</v>
       </c>
       <c r="F409" t="str">
-        <v>16.67%</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410">
-        <v>81</v>
-      </c>
-      <c r="B410" t="str">
-        <v>Route 10</v>
-      </c>
-      <c r="C410" t="str">
-        <v/>
-      </c>
-      <c r="D410" t="str">
-        <v>Mandibuzz</v>
-      </c>
-      <c r="E410" t="str">
-        <v>88-89</v>
-      </c>
-      <c r="F410" t="str">
-        <v>16.67%</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411">
-        <v>81</v>
-      </c>
-      <c r="B411" t="str">
-        <v>Route 10</v>
-      </c>
-      <c r="C411" t="str">
-        <v/>
-      </c>
-      <c r="D411" t="str">
-        <v>Amoonguss</v>
-      </c>
-      <c r="E411" t="str">
-        <v>88-89</v>
-      </c>
-      <c r="F411" t="str">
-        <v>16.67%</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412">
-        <v>81</v>
-      </c>
-      <c r="B412" t="str">
-        <v>Route 10</v>
-      </c>
-      <c r="C412" t="str">
-        <v/>
-      </c>
-      <c r="D412" t="str">
-        <v>Eelektrik</v>
-      </c>
-      <c r="E412" t="str">
-        <v>88-89</v>
-      </c>
-      <c r="F412" t="str">
-        <v>16.67%</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413">
-        <v>81</v>
-      </c>
-      <c r="B413" t="str">
-        <v>Route 10</v>
-      </c>
-      <c r="C413" t="str">
-        <v/>
-      </c>
-      <c r="D413" t="str">
-        <v>Vullaby</v>
-      </c>
-      <c r="E413" t="str">
-        <v>88-89</v>
-      </c>
-      <c r="F413" t="str">
-        <v>16.67%</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414">
-        <v>82</v>
-      </c>
-      <c r="B414" t="str">
-        <v>Abundant Shrine Depths</v>
-      </c>
-      <c r="C414" t="str">
-        <v/>
-      </c>
-      <c r="D414" t="str">
-        <v>Landorus</v>
-      </c>
-      <c r="E414" t="str">
-        <v>110</v>
-      </c>
-      <c r="F414" t="str">
-        <v>33.34%</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415">
-        <v>82</v>
-      </c>
-      <c r="B415" t="str">
-        <v>Abundant Shrine Depths</v>
-      </c>
-      <c r="C415" t="str">
-        <v/>
-      </c>
-      <c r="D415" t="str">
-        <v>Thundurus</v>
-      </c>
-      <c r="E415" t="str">
-        <v>110</v>
-      </c>
-      <c r="F415" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416">
-        <v>82</v>
-      </c>
-      <c r="B416" t="str">
-        <v>Abundant Shrine Depths</v>
-      </c>
-      <c r="C416" t="str">
-        <v/>
-      </c>
-      <c r="D416" t="str">
-        <v>Tornadus</v>
-      </c>
-      <c r="E416" t="str">
-        <v>110</v>
-      </c>
-      <c r="F416" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417">
-        <v>83</v>
-      </c>
-      <c r="B417" t="str">
-        <v>Dragonspire Clouds</v>
-      </c>
-      <c r="C417" t="str">
-        <v/>
-      </c>
-      <c r="D417" t="str">
-        <v>Kyurem</v>
-      </c>
-      <c r="E417" t="str">
-        <v>120-121</v>
-      </c>
-      <c r="F417" t="str">
-        <v>33.34%</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418">
-        <v>83</v>
-      </c>
-      <c r="B418" t="str">
-        <v>Dragonspire Clouds</v>
-      </c>
-      <c r="C418" t="str">
-        <v/>
-      </c>
-      <c r="D418" t="str">
-        <v>Reshiram</v>
-      </c>
-      <c r="E418" t="str">
-        <v>120-121</v>
-      </c>
-      <c r="F418" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419">
-        <v>83</v>
-      </c>
-      <c r="B419" t="str">
-        <v>Dragonspire Clouds</v>
-      </c>
-      <c r="C419" t="str">
-        <v/>
-      </c>
-      <c r="D419" t="str">
-        <v>Zekrom</v>
-      </c>
-      <c r="E419" t="str">
-        <v>120-121</v>
-      </c>
-      <c r="F419" t="str">
         <v>33.33%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F419"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F409"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9350,7 +9150,7 @@
         <v>Defeat Trainer in Route 22</v>
       </c>
       <c r="C51" t="str">
-        <v>Unlock Giant Chasm</v>
+        <v>Unlock P2 Laboratory</v>
       </c>
     </row>
     <row r="52">
@@ -9358,10 +9158,10 @@
         <v>Challenge 51</v>
       </c>
       <c r="B52" t="str">
-        <v>Defeat Trainer in Giant Chasm</v>
+        <v>Defeat Trainer in P2 Laboratory</v>
       </c>
       <c r="C52" t="str">
-        <v>Unlock Route 23</v>
+        <v>Unlock Wellspring Cave</v>
       </c>
     </row>
     <row r="53">
@@ -9369,10 +9169,10 @@
         <v>Challenge 52</v>
       </c>
       <c r="B53" t="str">
-        <v>Defeat Trainer in Route 23</v>
+        <v>Defeat Trainer in Wellspring Cave</v>
       </c>
       <c r="C53" t="str">
-        <v>Unlock Victory Road</v>
+        <v>Unlock Giant Chasm</v>
       </c>
     </row>
     <row r="54">
@@ -9380,117 +9180,117 @@
         <v>Challenge 53</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat Trainer in Victory Road</v>
+        <v>Defeat Trainer in Giant Chasm</v>
       </c>
       <c r="C54" t="str">
-        <v>Unlock Pokemon League</v>
+        <v>Unlock Route 23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="B55" t="str">
-        <v>Complete Challenge 53</v>
+        <v>Defeat Trainer in Route 23</v>
       </c>
       <c r="C55" t="str">
-        <v>Unlock Route 8</v>
+        <v>Unlock Victory Road</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Extra Challenge A 1</v>
+        <v>Challenge 55</v>
       </c>
       <c r="B56" t="str">
-        <v>Catch 10 Pokemon in Route 8</v>
+        <v>Defeat Trainer in Victory Road</v>
       </c>
       <c r="C56" t="str">
-        <v>Unlock Moor of Icirrus</v>
+        <v>Unlock Pokemon League</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Extra Challenge A 2</v>
+        <v/>
       </c>
       <c r="B57" t="str">
-        <v>Catch 10 Pokemon in Moor of Icirrus</v>
+        <v>Complete Challenge 20</v>
       </c>
       <c r="C57" t="str">
-        <v>Unlock Icirrus City</v>
+        <v>Unlock Route 8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Extra Challenge A 3</v>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B58" t="str">
-        <v>Visit Icirrus City</v>
+        <v>Catch 10 Pokemon in Route 8</v>
       </c>
       <c r="C58" t="str">
-        <v>Unlock Dragonspiral Tower</v>
+        <v>Unlock Moor of Icirrus</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extra Challenge A 4</v>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B59" t="str">
-        <v>Catch 10 Pokemon in Dragonspiral Tower</v>
+        <v>Catch 10 Pokemon in Moor of Icirrus</v>
       </c>
       <c r="C59" t="str">
-        <v>Unlock Moor of Icirrus Depths</v>
+        <v>Unlock Icirrus City</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B60" t="str">
-        <v>Complete Challenge 53</v>
+        <v>Visit Icirrus City</v>
       </c>
       <c r="C60" t="str">
-        <v>Unlock Twist Mountain</v>
+        <v>Unlock Dragonspiral Tower</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Extra Challenge B 1</v>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B61" t="str">
-        <v>Catch 10 Pokemon in Twist Mountain</v>
+        <v>Catch 10 Pokemon in Dragonspiral Tower</v>
       </c>
       <c r="C61" t="str">
-        <v>Unlock Underground Ruins</v>
+        <v>Unlock Twist Mountain</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Extra Challenge B 2</v>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B62" t="str">
-        <v>Catch 10 Pokemon in Underground Ruins</v>
+        <v>Catch 10 Pokemon in Twist Mountain</v>
       </c>
       <c r="C62" t="str">
-        <v>Unlock Route 15</v>
+        <v>Unlock Underground Ruins</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extra Challenge B 3</v>
+        <v/>
       </c>
       <c r="B63" t="str">
-        <v>Catch 10 Pokemon in Route 15</v>
+        <v>Complete Challenge 31</v>
       </c>
       <c r="C63" t="str">
-        <v>Unlock Route 16</v>
+        <v>Unlock Route 15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Extra Challenge B 4</v>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B64" t="str">
-        <v>Catch 10 Pokemon in Route 16</v>
+        <v>Catch 10 Pokemon in Route 15</v>
       </c>
       <c r="C64" t="str">
         <v>Unlock Striaton City</v>
@@ -9498,7 +9298,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extra Challenge B 5</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B65" t="str">
         <v>Visit Striaton City</v>
@@ -9509,10 +9309,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B66" t="str">
-        <v>Complete Challenge 53</v>
+        <v>Catch 10 Pokemon in Dreamyard</v>
       </c>
       <c r="C66" t="str">
         <v>Unlock Route 18</v>
@@ -9520,175 +9320,175 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Extra Challenge C 1</v>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B67" t="str">
         <v>Catch 10 Pokemon in Route 18</v>
       </c>
       <c r="C67" t="str">
-        <v>Unlock P2 Laboratory</v>
+        <v>Unlock Route 17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Extra Challenge C 2</v>
+        <v/>
       </c>
       <c r="B68" t="str">
-        <v>Catch 10 Pokemon in P2 Laboratory</v>
+        <v>Complete Challenge null</v>
       </c>
       <c r="C68" t="str">
-        <v>Unlock Route 17</v>
+        <v>Unlock Route 1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Extra Challenge C 3</v>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B69" t="str">
-        <v>Catch 10 Pokemon in Route 17</v>
+        <v>Catch 10 Pokemon in Route 1</v>
       </c>
       <c r="C69" t="str">
-        <v>Unlock Cave of Being</v>
+        <v>Unlock Nuvema Town</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Extra Challenge C 4</v>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B70" t="str">
-        <v>Catch 10 Pokemon in Cave of Being</v>
+        <v>Visit Nuvema Town</v>
       </c>
       <c r="C70" t="str">
-        <v>Unlock Nature Sanctuary</v>
+        <v>Unlock Route 2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Extra Challenge C 5</v>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="B71" t="str">
-        <v>Catch 10 Pokemon in Nature Sanctuary</v>
+        <v>Catch 10 Pokemon in Route 2</v>
       </c>
       <c r="C71" t="str">
-        <v>Unlock Liberty Garden</v>
+        <v>Unlock Route 3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="B72" t="str">
-        <v>Complete Challenge 53</v>
+        <v>Catch 10 Pokemon in Route 3</v>
       </c>
       <c r="C72" t="str">
-        <v>Unlock Route 1</v>
+        <v>Unlock Moor of Icirrus Depths</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Extra Challenge D 1</v>
+        <v/>
       </c>
       <c r="B73" t="str">
-        <v>Catch 10 Pokemon in Route 1</v>
+        <v>Complete Challenge null</v>
       </c>
       <c r="C73" t="str">
-        <v>Unlock Nuvema Town</v>
+        <v>Unlock Daycare</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Extra Challenge D 2</v>
+        <v>Extra Challenge D 1</v>
       </c>
       <c r="B74" t="str">
-        <v>Visit Nuvema Town</v>
+        <v>Visit Daycare</v>
       </c>
       <c r="C74" t="str">
-        <v>Unlock Route 2</v>
+        <v>Unlock Nacrene City</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Extra Challenge D 3</v>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="B75" t="str">
-        <v>Catch 10 Pokemon in Route 2</v>
+        <v>Visit Nacrene City</v>
       </c>
       <c r="C75" t="str">
-        <v>Unlock Route 3</v>
+        <v>Unlock Pinwheel Forest</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Extra Challenge D 4</v>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="B76" t="str">
-        <v>Catch 10 Pokemon in Route 3</v>
+        <v>Catch 10 Pokemon in Pinwheel Forest</v>
       </c>
       <c r="C76" t="str">
-        <v>Unlock Daycare</v>
+        <v>Unlock Cave of Being</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Extra Challenge D 5</v>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="B77" t="str">
-        <v>Catch 10 Pokemon in Daycare</v>
+        <v>Catch 10 Pokemon in Cave of Being</v>
       </c>
       <c r="C77" t="str">
-        <v>Unlock Nacrene City</v>
+        <v>Unlock Liberty Garden</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Extra Challenge D 6</v>
+        <v/>
       </c>
       <c r="B78" t="str">
-        <v>Visit Nacrene City</v>
+        <v>Complete Challenge null</v>
       </c>
       <c r="C78" t="str">
-        <v>Unlock Pinwheel Forest</v>
+        <v>Unlock Route 10</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Extra Challenge D 7</v>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="B79" t="str">
-        <v>Catch 10 Pokemon in Pinwheel Forest</v>
+        <v>Catch 10 Pokemon in Route 10</v>
       </c>
       <c r="C79" t="str">
-        <v>Unlock Wellspring Cave</v>
+        <v>Unlock Nature Sanctuary</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="B80" t="str">
-        <v>Complete Challenge 53</v>
+        <v>Catch 10 Pokemon in Nature Sanctuary</v>
       </c>
       <c r="C80" t="str">
-        <v>Unlock Driftveil Drawbridge</v>
+        <v>Unlock Route 24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Extra Challenge E 1</v>
+        <v>Extra Challenge E 3</v>
       </c>
       <c r="B81" t="str">
-        <v>Catch 10 Pokemon in Driftveil Drawbridge</v>
+        <v>Catch 10 Pokemon in Route 24</v>
       </c>
       <c r="C81" t="str">
-        <v>Unlock Route 10</v>
+        <v>Unlock Route 25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Extra Challenge E 2</v>
+        <v>Extra Challenge E 4</v>
       </c>
       <c r="B82" t="str">
-        <v>Catch 10 Pokemon in Route 10</v>
+        <v>Catch 10 Pokemon in Route 25</v>
       </c>
       <c r="C82" t="str">
         <v>Unlock Abundant Shrine Depths</v>
@@ -9699,2235 +9499,25 @@
         <v>Condition to Final Challenge</v>
       </c>
       <c r="B83" t="str">
-        <v>Complete Extra Challenge A 4, B 5, C 5, D 7, and E 2</v>
+        <v>Complete Extra Challenge A 5, B 4, C 4, D 4, E 4</v>
       </c>
       <c r="C83" t="str">
         <v>Unlock Dragonspire Clouds</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Final Challenge</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Catch 1 Kyurem 1 Reshiram 1 Zekrom</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Unlock True Ending</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C83"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D157"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Pokemon Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Pokemon Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Path to be include</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Obtained?</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Snivy</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D2" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Servine</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Serperior</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Tepig</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D5" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Pignite</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Emboar</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Oshawott</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D8" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Dewott</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Samurott</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Patrat</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D11" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Watchog</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Lillipup</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D13" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Herdier</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Stoutland</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Purrloin</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D16" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Liepard</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Pansage</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D18" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Simisage</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Pansear</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D20" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Simisear</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Panpour</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D22" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Simipour</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Munna</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D24" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Musharna</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Pidove</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D26" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Tranquill</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Unfezant</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Blitzle</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D29" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Zebstrika</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Roggenrola</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D31" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Boldore</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Gigalith</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Woobat</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D34" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Swoobat</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Drilbur</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D36" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Excadrill</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Audino</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D38" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Timburr</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D39" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Gurdurr</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Conkeldurr</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Tympole</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D42" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Palpitoad</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Seismitoad</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Throh</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D45" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Sawk</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D46" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Sewaddle</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D47" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Swadloon</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Leavanny</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Venipede</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D50" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Whirlipede</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Scolipede</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Cottonee</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D53" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Whimsicott</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D54" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Petilil</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D55" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Lilligant</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Basculin</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D57" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Sandile</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D58" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Krokorok</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D59" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Krookodile</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D60" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Darumaka</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D61" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Darmanitan</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D62" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Maractus</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D63" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Dwebble</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D64" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Crustle</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D65" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Scraggy</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D66" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Scrafty</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D67" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Sigilyph</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D68" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Yamask</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D69" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Cofagrigus</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D70" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Tirtouga</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D71" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Carracosta</v>
-      </c>
-      <c r="B72" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C72" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D72" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Archen</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C73" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D73" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Archeops</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C74" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D74" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Trubbish</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D75" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Garbodor</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D76" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Zorua</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D77" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Zoroark</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C78" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D78" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Minccino</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D79" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Cinccino</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D80" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Gothita</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D81" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Gothorita</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D82" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Gothitelle</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D83" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Solosis</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D84" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Duosion</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Reuniclus</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D86" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Ducklett</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D87" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Swanna</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D88" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Vanillite</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D89" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Vanillish</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D90" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Vanilluxe</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D91" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Deerling</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D92" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Sawsbuck</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D93" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Emolga</v>
-      </c>
-      <c r="B94" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D94" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Karrablast</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D95" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Escavalier</v>
-      </c>
-      <c r="B96" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D96" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Foongus</v>
-      </c>
-      <c r="B97" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D97" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Amoonguss</v>
-      </c>
-      <c r="B98" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D98" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Frillish</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D99" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Jellicent</v>
-      </c>
-      <c r="B100" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D100" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Alomomola</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D101" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Joltik</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D102" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Galvantula</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D103" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Ferroseed</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D104" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Ferrothorn</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Klink</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D106" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Klang</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D107" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>Klinklang</v>
-      </c>
-      <c r="B108" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D108" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Tynamo</v>
-      </c>
-      <c r="B109" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C109" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D109" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>Eelektrik</v>
-      </c>
-      <c r="B110" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C110" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D110" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>Eelektross</v>
-      </c>
-      <c r="B111" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C111" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D111" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>Elgyem</v>
-      </c>
-      <c r="B112" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C112" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D112" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Beheeyem</v>
-      </c>
-      <c r="B113" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C113" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>Litwick</v>
-      </c>
-      <c r="B114" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C114" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D114" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>Lampent</v>
-      </c>
-      <c r="B115" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D115" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>Chandelure</v>
-      </c>
-      <c r="B116" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C116" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D116" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>Axew</v>
-      </c>
-      <c r="B117" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C117" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D117" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>Fraxure</v>
-      </c>
-      <c r="B118" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C118" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D118" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>Haxorus</v>
-      </c>
-      <c r="B119" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C119" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D119" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>Cubchoo</v>
-      </c>
-      <c r="B120" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C120" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D120" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>Beartic</v>
-      </c>
-      <c r="B121" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C121" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D121" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>Cryogonal</v>
-      </c>
-      <c r="B122" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C122" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D122" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>Shelmet</v>
-      </c>
-      <c r="B123" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C123" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D123" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>Accelgor</v>
-      </c>
-      <c r="B124" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C124" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D124" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>Stunfisk</v>
-      </c>
-      <c r="B125" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C125" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D125" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>Mienfoo</v>
-      </c>
-      <c r="B126" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C126" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D126" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>Mienshao</v>
-      </c>
-      <c r="B127" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C127" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D127" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>Druddigon</v>
-      </c>
-      <c r="B128" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C128" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D128" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Golett</v>
-      </c>
-      <c r="B129" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C129" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D129" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>Golurk</v>
-      </c>
-      <c r="B130" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C130" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D130" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>Pawniard</v>
-      </c>
-      <c r="B131" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C131" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D131" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>Bisharp</v>
-      </c>
-      <c r="B132" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C132" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D132" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>Bouffalant</v>
-      </c>
-      <c r="B133" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C133" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D133" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>Rufflet</v>
-      </c>
-      <c r="B134" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C134" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D134" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>Braviary</v>
-      </c>
-      <c r="B135" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C135" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D135" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>Vullaby</v>
-      </c>
-      <c r="B136" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C136" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D136" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>Mandibuzz</v>
-      </c>
-      <c r="B137" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C137" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D137" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>Heatmor</v>
-      </c>
-      <c r="B138" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C138" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D138" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>Durant</v>
-      </c>
-      <c r="B139" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C139" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D139" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>Deino</v>
-      </c>
-      <c r="B140" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C140" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D140" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>Zweilous</v>
-      </c>
-      <c r="B141" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C141" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D141" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>Hydreigon</v>
-      </c>
-      <c r="B142" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C142" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D142" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>Larvesta</v>
-      </c>
-      <c r="B143" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C143" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D143" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>Volcarona</v>
-      </c>
-      <c r="B144" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C144" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D144" t="str">
-        <v>Yes (Obtainable via Evolution)</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>Cobalion</v>
-      </c>
-      <c r="B145" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C145" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D145" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>Terrakion</v>
-      </c>
-      <c r="B146" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C146" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D146" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>Virizion</v>
-      </c>
-      <c r="B147" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C147" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D147" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>Tornadus</v>
-      </c>
-      <c r="B148" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C148" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D148" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>Thundurus</v>
-      </c>
-      <c r="B149" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C149" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D149" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>Reshiram</v>
-      </c>
-      <c r="B150" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C150" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D150" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>Zekrom</v>
-      </c>
-      <c r="B151" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C151" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D151" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Landorus</v>
-      </c>
-      <c r="B152" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C152" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D152" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Kyurem</v>
-      </c>
-      <c r="B153" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C153" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D153" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>Keldeo</v>
-      </c>
-      <c r="B154" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C154" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D154" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>Meloetta</v>
-      </c>
-      <c r="B155" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C155" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D155" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>Genesect</v>
-      </c>
-      <c r="B156" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C156" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D156" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>Victini</v>
-      </c>
-      <c r="B157" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="C157" t="str">
-        <v>Already Placed or Obtainable</v>
-      </c>
-      <c r="D157" t="str">
-        <v>No (Placed)</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>